--- a/data/salut_sabadell.xlsx
+++ b/data/salut_sabadell.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resum per Font" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Salut Sabadell'!$A$1:$Q$482</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Resum per Grup'!$A$1:$B$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Salut Sabadell'!$A$1:$Q$583</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Resum per Grup'!$A$1:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Resum per Barri'!$A$1:$C$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Resum per Font'!$A$1:$B$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Resum per Font'!$A$1:$B$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -446,12 +446,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q482"/>
+  <dimension ref="A1:Q583"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="27" customWidth="1" min="6" max="6"/>
@@ -32439,32 +32439,44 @@
     </row>
     <row r="468">
       <c r="A468" s="2" t="inlineStr"/>
-      <c r="B468" s="2" t="inlineStr"/>
-      <c r="C468" s="2" t="inlineStr"/>
+      <c r="B468" s="2" t="inlineStr">
+        <is>
+          <t>Juvenal</t>
+        </is>
+      </c>
+      <c r="C468" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="D468" s="2" t="inlineStr">
         <is>
-          <t>Centre d'Atenció Primària Sant Oleguer</t>
+          <t>Farmàcia I. Herrero Torres</t>
         </is>
       </c>
       <c r="E468" s="2" t="inlineStr">
         <is>
-          <t>Salut - Medicina</t>
-        </is>
-      </c>
-      <c r="F468" s="2" t="inlineStr"/>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="F468" s="2" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
       <c r="G468" s="2" t="inlineStr">
         <is>
-          <t>Activitats de medicina especialitzada</t>
+          <t>Farmàcies</t>
         </is>
       </c>
       <c r="H468" s="2" t="inlineStr">
         <is>
-          <t>41.5385552</t>
+          <t>41.553</t>
         </is>
       </c>
       <c r="I468" s="2" t="inlineStr">
         <is>
-          <t>2.1179282</t>
+          <t>2.0845</t>
         </is>
       </c>
       <c r="J468" s="2" t="inlineStr"/>
@@ -32472,46 +32484,58 @@
       <c r="L468" s="2" t="inlineStr"/>
       <c r="M468" s="2" t="inlineStr">
         <is>
-          <t>OSM_2026</t>
+          <t>farmacias_2026</t>
         </is>
       </c>
       <c r="N468" s="2" t="inlineStr"/>
-      <c r="O468" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P468" s="2" t="inlineStr"/>
+      <c r="O468" s="2" t="inlineStr"/>
+      <c r="P468" s="2" t="inlineStr">
+        <is>
+          <t>Juvenal 12</t>
+        </is>
+      </c>
       <c r="Q468" s="2" t="inlineStr"/>
     </row>
     <row r="469">
       <c r="A469" s="3" t="inlineStr"/>
-      <c r="B469" s="3" t="inlineStr"/>
-      <c r="C469" s="3" t="inlineStr"/>
+      <c r="B469" s="3" t="inlineStr">
+        <is>
+          <t>Colom</t>
+        </is>
+      </c>
+      <c r="C469" s="3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="D469" s="3" t="inlineStr">
         <is>
-          <t>Asepeyo</t>
+          <t>Farmàcia A. Crusafont Sabaté</t>
         </is>
       </c>
       <c r="E469" s="3" t="inlineStr">
         <is>
-          <t>Salut - Medicina</t>
-        </is>
-      </c>
-      <c r="F469" s="3" t="inlineStr"/>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="F469" s="3" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
       <c r="G469" s="3" t="inlineStr">
         <is>
-          <t>Activitats de medicina especialitzada</t>
+          <t>Farmàcies</t>
         </is>
       </c>
       <c r="H469" s="3" t="inlineStr">
         <is>
-          <t>41.5447489</t>
+          <t>41.5485</t>
         </is>
       </c>
       <c r="I469" s="3" t="inlineStr">
         <is>
-          <t>2.1002579</t>
+          <t>2.109</t>
         </is>
       </c>
       <c r="J469" s="3" t="inlineStr"/>
@@ -32519,46 +32543,58 @@
       <c r="L469" s="3" t="inlineStr"/>
       <c r="M469" s="3" t="inlineStr">
         <is>
-          <t>OSM_2026</t>
+          <t>farmacias_2026</t>
         </is>
       </c>
       <c r="N469" s="3" t="inlineStr"/>
-      <c r="O469" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P469" s="3" t="inlineStr"/>
+      <c r="O469" s="3" t="inlineStr"/>
+      <c r="P469" s="3" t="inlineStr">
+        <is>
+          <t>Colom 13</t>
+        </is>
+      </c>
       <c r="Q469" s="3" t="inlineStr"/>
     </row>
     <row r="470">
       <c r="A470" s="2" t="inlineStr"/>
-      <c r="B470" s="2" t="inlineStr"/>
-      <c r="C470" s="2" t="inlineStr"/>
+      <c r="B470" s="2" t="inlineStr">
+        <is>
+          <t>Plaça de Llívia</t>
+        </is>
+      </c>
+      <c r="C470" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D470" s="2" t="inlineStr">
         <is>
-          <t>C.A.P. Sant Fèlix</t>
+          <t>Farmàcia I. Domènech Sagué</t>
         </is>
       </c>
       <c r="E470" s="2" t="inlineStr">
         <is>
-          <t>Salut - Medicina</t>
-        </is>
-      </c>
-      <c r="F470" s="2" t="inlineStr"/>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="F470" s="2" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
       <c r="G470" s="2" t="inlineStr">
         <is>
-          <t>Activitats de medicina especialitzada</t>
+          <t>Farmàcies</t>
         </is>
       </c>
       <c r="H470" s="2" t="inlineStr">
         <is>
-          <t>41.5325822</t>
+          <t>41.564</t>
         </is>
       </c>
       <c r="I470" s="2" t="inlineStr">
         <is>
-          <t>2.1139605</t>
+          <t>2.0905</t>
         </is>
       </c>
       <c r="J470" s="2" t="inlineStr"/>
@@ -32566,50 +32602,58 @@
       <c r="L470" s="2" t="inlineStr"/>
       <c r="M470" s="2" t="inlineStr">
         <is>
-          <t>OSM_2026</t>
+          <t>farmacias_2026</t>
         </is>
       </c>
       <c r="N470" s="2" t="inlineStr"/>
-      <c r="O470" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P470" s="2" t="inlineStr"/>
+      <c r="O470" s="2" t="inlineStr"/>
+      <c r="P470" s="2" t="inlineStr">
+        <is>
+          <t>Plaça de Llívia 1</t>
+        </is>
+      </c>
       <c r="Q470" s="2" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" s="3" t="inlineStr"/>
-      <c r="B471" s="3" t="inlineStr"/>
-      <c r="C471" s="3" t="inlineStr"/>
+      <c r="B471" s="3" t="inlineStr">
+        <is>
+          <t>Flamisell</t>
+        </is>
+      </c>
+      <c r="C471" s="3" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
       <c r="D471" s="3" t="inlineStr">
         <is>
-          <t>Multiópticas</t>
+          <t>Farmàcia M. Vilaltella Coll</t>
         </is>
       </c>
       <c r="E471" s="3" t="inlineStr">
         <is>
-          <t>Salut - Òptica</t>
+          <t>Farmàcies</t>
         </is>
       </c>
       <c r="F471" s="3" t="inlineStr">
         <is>
-          <t>optician</t>
+          <t>WebSearch</t>
         </is>
       </c>
       <c r="G471" s="3" t="inlineStr">
         <is>
-          <t>Òptica</t>
+          <t>Farmàcies</t>
         </is>
       </c>
       <c r="H471" s="3" t="inlineStr">
         <is>
-          <t>41.5412052</t>
+          <t>41.5475</t>
         </is>
       </c>
       <c r="I471" s="3" t="inlineStr">
         <is>
-          <t>2.1117753</t>
+          <t>2.107</t>
         </is>
       </c>
       <c r="J471" s="3" t="inlineStr"/>
@@ -32617,50 +32661,58 @@
       <c r="L471" s="3" t="inlineStr"/>
       <c r="M471" s="3" t="inlineStr">
         <is>
-          <t>OSM</t>
+          <t>farmacias_2026</t>
         </is>
       </c>
       <c r="N471" s="3" t="inlineStr"/>
-      <c r="O471" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P471" s="3" t="inlineStr"/>
+      <c r="O471" s="3" t="inlineStr"/>
+      <c r="P471" s="3" t="inlineStr">
+        <is>
+          <t>Flamisell 55</t>
+        </is>
+      </c>
       <c r="Q471" s="3" t="inlineStr"/>
     </row>
     <row r="472">
       <c r="A472" s="2" t="inlineStr"/>
-      <c r="B472" s="2" t="inlineStr"/>
-      <c r="C472" s="2" t="inlineStr"/>
+      <c r="B472" s="2" t="inlineStr">
+        <is>
+          <t>Carretera de Barcelona</t>
+        </is>
+      </c>
+      <c r="C472" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
       <c r="D472" s="2" t="inlineStr">
         <is>
-          <t>Visionlab</t>
+          <t>Farmàcia J. Marcet Vicens</t>
         </is>
       </c>
       <c r="E472" s="2" t="inlineStr">
         <is>
-          <t>Salut - Òptica</t>
+          <t>Farmàcies</t>
         </is>
       </c>
       <c r="F472" s="2" t="inlineStr">
         <is>
-          <t>optician</t>
+          <t>WebSearch</t>
         </is>
       </c>
       <c r="G472" s="2" t="inlineStr">
         <is>
-          <t>Òptica</t>
+          <t>Farmàcies</t>
         </is>
       </c>
       <c r="H472" s="2" t="inlineStr">
         <is>
-          <t>41.5535969</t>
+          <t>41.553</t>
         </is>
       </c>
       <c r="I472" s="2" t="inlineStr">
         <is>
-          <t>2.0985035</t>
+          <t>2.0875</t>
         </is>
       </c>
       <c r="J472" s="2" t="inlineStr"/>
@@ -32668,30 +32720,38 @@
       <c r="L472" s="2" t="inlineStr"/>
       <c r="M472" s="2" t="inlineStr">
         <is>
-          <t>OSM</t>
+          <t>farmacias_2026</t>
         </is>
       </c>
       <c r="N472" s="2" t="inlineStr"/>
-      <c r="O472" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P472" s="2" t="inlineStr"/>
+      <c r="O472" s="2" t="inlineStr"/>
+      <c r="P472" s="2" t="inlineStr">
+        <is>
+          <t>Carretera de Barcelona 74</t>
+        </is>
+      </c>
       <c r="Q472" s="2" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" s="3" t="inlineStr"/>
-      <c r="B473" s="3" t="inlineStr"/>
-      <c r="C473" s="3" t="inlineStr"/>
+      <c r="B473" s="3" t="inlineStr">
+        <is>
+          <t>Passeig de Plaça Major</t>
+        </is>
+      </c>
+      <c r="C473" s="3" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
       <c r="D473" s="3" t="inlineStr">
         <is>
-          <t>FIOSTEC Funcional Sabadell</t>
+          <t>Farmàcia J. Llop Talaveró</t>
         </is>
       </c>
       <c r="E473" s="3" t="inlineStr">
         <is>
-          <t>Salut - Fisioterapia</t>
+          <t>Farmàcies</t>
         </is>
       </c>
       <c r="F473" s="3" t="inlineStr">
@@ -32701,48 +32761,56 @@
       </c>
       <c r="G473" s="3" t="inlineStr">
         <is>
-          <t>Salut - Fisioterapia</t>
+          <t>Farmàcies</t>
         </is>
       </c>
       <c r="H473" s="3" t="inlineStr">
         <is>
-          <t>41.5485</t>
+          <t>41.5475</t>
         </is>
       </c>
       <c r="I473" s="3" t="inlineStr">
         <is>
-          <t>2.109</t>
-        </is>
-      </c>
-      <c r="J473" s="3" t="inlineStr">
-        <is>
-          <t>fiostec.com</t>
-        </is>
-      </c>
+          <t>2.107</t>
+        </is>
+      </c>
+      <c r="J473" s="3" t="inlineStr"/>
       <c r="K473" s="3" t="inlineStr"/>
       <c r="L473" s="3" t="inlineStr"/>
       <c r="M473" s="3" t="inlineStr">
         <is>
-          <t>WebSearch_2026</t>
+          <t>farmacias_2026</t>
         </is>
       </c>
       <c r="N473" s="3" t="inlineStr"/>
       <c r="O473" s="3" t="inlineStr"/>
-      <c r="P473" s="3" t="inlineStr"/>
+      <c r="P473" s="3" t="inlineStr">
+        <is>
+          <t>Passeig de Plaça Major 58</t>
+        </is>
+      </c>
       <c r="Q473" s="3" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" s="2" t="inlineStr"/>
-      <c r="B474" s="2" t="inlineStr"/>
-      <c r="C474" s="2" t="inlineStr"/>
+      <c r="B474" s="2" t="inlineStr">
+        <is>
+          <t>Ronda Zamenhof</t>
+        </is>
+      </c>
+      <c r="C474" s="2" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
       <c r="D474" s="2" t="inlineStr">
         <is>
-          <t>Fisioterapia i Osteopatia Sabadell</t>
+          <t>Farmàcia J. Pareja Cozcolluela</t>
         </is>
       </c>
       <c r="E474" s="2" t="inlineStr">
         <is>
-          <t>Salut - Fisioterapia</t>
+          <t>Farmàcies</t>
         </is>
       </c>
       <c r="F474" s="2" t="inlineStr">
@@ -32752,7 +32820,7 @@
       </c>
       <c r="G474" s="2" t="inlineStr">
         <is>
-          <t>Salut - Fisioterapia</t>
+          <t>Farmàcies</t>
         </is>
       </c>
       <c r="H474" s="2" t="inlineStr">
@@ -32765,35 +32833,43 @@
           <t>2.109</t>
         </is>
       </c>
-      <c r="J474" s="2" t="inlineStr">
-        <is>
-          <t>fisioterapiaiosteopatia.net</t>
-        </is>
-      </c>
+      <c r="J474" s="2" t="inlineStr"/>
       <c r="K474" s="2" t="inlineStr"/>
       <c r="L474" s="2" t="inlineStr"/>
       <c r="M474" s="2" t="inlineStr">
         <is>
-          <t>WebSearch_2026</t>
+          <t>farmacias_2026</t>
         </is>
       </c>
       <c r="N474" s="2" t="inlineStr"/>
       <c r="O474" s="2" t="inlineStr"/>
-      <c r="P474" s="2" t="inlineStr"/>
+      <c r="P474" s="2" t="inlineStr">
+        <is>
+          <t>Ronda Zamenhof 145</t>
+        </is>
+      </c>
       <c r="Q474" s="2" t="inlineStr"/>
     </row>
     <row r="475">
       <c r="A475" s="3" t="inlineStr"/>
-      <c r="B475" s="3" t="inlineStr"/>
-      <c r="C475" s="3" t="inlineStr"/>
+      <c r="B475" s="3" t="inlineStr">
+        <is>
+          <t>Pasteral</t>
+        </is>
+      </c>
+      <c r="C475" s="3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="D475" s="3" t="inlineStr">
         <is>
-          <t>PsicoSabadell</t>
+          <t>Farmàcia E. Álvarez Pereiro</t>
         </is>
       </c>
       <c r="E475" s="3" t="inlineStr">
         <is>
-          <t>Salut - Psicologia</t>
+          <t>Farmàcies</t>
         </is>
       </c>
       <c r="F475" s="3" t="inlineStr">
@@ -32803,48 +32879,56 @@
       </c>
       <c r="G475" s="3" t="inlineStr">
         <is>
-          <t>Salut - Psicologia</t>
+          <t>Farmàcies</t>
         </is>
       </c>
       <c r="H475" s="3" t="inlineStr">
         <is>
-          <t>41.5485</t>
+          <t>41.5475</t>
         </is>
       </c>
       <c r="I475" s="3" t="inlineStr">
         <is>
-          <t>2.109</t>
-        </is>
-      </c>
-      <c r="J475" s="3" t="inlineStr">
-        <is>
-          <t>psicosabadell.com</t>
-        </is>
-      </c>
+          <t>2.107</t>
+        </is>
+      </c>
+      <c r="J475" s="3" t="inlineStr"/>
       <c r="K475" s="3" t="inlineStr"/>
       <c r="L475" s="3" t="inlineStr"/>
       <c r="M475" s="3" t="inlineStr">
         <is>
-          <t>WebSearch_2026</t>
+          <t>farmacias_2026</t>
         </is>
       </c>
       <c r="N475" s="3" t="inlineStr"/>
       <c r="O475" s="3" t="inlineStr"/>
-      <c r="P475" s="3" t="inlineStr"/>
+      <c r="P475" s="3" t="inlineStr">
+        <is>
+          <t>Pasteral 9</t>
+        </is>
+      </c>
       <c r="Q475" s="3" t="inlineStr"/>
     </row>
     <row r="476">
       <c r="A476" s="2" t="inlineStr"/>
-      <c r="B476" s="2" t="inlineStr"/>
-      <c r="C476" s="2" t="inlineStr"/>
+      <c r="B476" s="2" t="inlineStr">
+        <is>
+          <t>Carrer de Covadonga</t>
+        </is>
+      </c>
+      <c r="C476" s="2" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
       <c r="D476" s="2" t="inlineStr">
         <is>
-          <t>Psicologia Clínica Sabadell</t>
+          <t>Farmàcia X. Fernández Toirán</t>
         </is>
       </c>
       <c r="E476" s="2" t="inlineStr">
         <is>
-          <t>Salut - Psicologia</t>
+          <t>Farmàcies</t>
         </is>
       </c>
       <c r="F476" s="2" t="inlineStr">
@@ -32854,48 +32938,56 @@
       </c>
       <c r="G476" s="2" t="inlineStr">
         <is>
-          <t>Salut - Psicologia</t>
+          <t>Farmàcies</t>
         </is>
       </c>
       <c r="H476" s="2" t="inlineStr">
         <is>
-          <t>41.5485</t>
+          <t>41.5475</t>
         </is>
       </c>
       <c r="I476" s="2" t="inlineStr">
         <is>
-          <t>2.109</t>
-        </is>
-      </c>
-      <c r="J476" s="2" t="inlineStr">
-        <is>
-          <t>psicologiaclinicasabadell.es</t>
-        </is>
-      </c>
+          <t>2.107</t>
+        </is>
+      </c>
+      <c r="J476" s="2" t="inlineStr"/>
       <c r="K476" s="2" t="inlineStr"/>
       <c r="L476" s="2" t="inlineStr"/>
       <c r="M476" s="2" t="inlineStr">
         <is>
-          <t>WebSearch_2026</t>
+          <t>farmacias_2026</t>
         </is>
       </c>
       <c r="N476" s="2" t="inlineStr"/>
       <c r="O476" s="2" t="inlineStr"/>
-      <c r="P476" s="2" t="inlineStr"/>
+      <c r="P476" s="2" t="inlineStr">
+        <is>
+          <t>Carrer de Covadonga 310</t>
+        </is>
+      </c>
       <c r="Q476" s="2" t="inlineStr"/>
     </row>
     <row r="477">
       <c r="A477" s="3" t="inlineStr"/>
-      <c r="B477" s="3" t="inlineStr"/>
-      <c r="C477" s="3" t="inlineStr"/>
+      <c r="B477" s="3" t="inlineStr">
+        <is>
+          <t>Carretera de Barcelona</t>
+        </is>
+      </c>
+      <c r="C477" s="3" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
       <c r="D477" s="3" t="inlineStr">
         <is>
-          <t>Psicologia i Educació Sabadell</t>
+          <t>Farmàcia G. Montané Bombardó</t>
         </is>
       </c>
       <c r="E477" s="3" t="inlineStr">
         <is>
-          <t>Salut - Psicologia</t>
+          <t>Farmàcies</t>
         </is>
       </c>
       <c r="F477" s="3" t="inlineStr">
@@ -32905,7 +32997,7 @@
       </c>
       <c r="G477" s="3" t="inlineStr">
         <is>
-          <t>Salut - Psicologia</t>
+          <t>Farmàcies</t>
         </is>
       </c>
       <c r="H477" s="3" t="inlineStr">
@@ -32918,35 +33010,43 @@
           <t>2.109</t>
         </is>
       </c>
-      <c r="J477" s="3" t="inlineStr">
-        <is>
-          <t>psicologiaieducaciosabadell.com</t>
-        </is>
-      </c>
+      <c r="J477" s="3" t="inlineStr"/>
       <c r="K477" s="3" t="inlineStr"/>
       <c r="L477" s="3" t="inlineStr"/>
       <c r="M477" s="3" t="inlineStr">
         <is>
-          <t>WebSearch_2026</t>
+          <t>farmacias_2026</t>
         </is>
       </c>
       <c r="N477" s="3" t="inlineStr"/>
       <c r="O477" s="3" t="inlineStr"/>
-      <c r="P477" s="3" t="inlineStr"/>
+      <c r="P477" s="3" t="inlineStr">
+        <is>
+          <t>Carretera de Barcelona 219</t>
+        </is>
+      </c>
       <c r="Q477" s="3" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" s="2" t="inlineStr"/>
-      <c r="B478" s="2" t="inlineStr"/>
-      <c r="C478" s="2" t="inlineStr"/>
+      <c r="B478" s="2" t="inlineStr">
+        <is>
+          <t>Carrer de Sol i Padrís</t>
+        </is>
+      </c>
+      <c r="C478" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
       <c r="D478" s="2" t="inlineStr">
         <is>
-          <t>Mèdic Dental Sabadell</t>
+          <t>Farmàcia A. Capdevila Bassols</t>
         </is>
       </c>
       <c r="E478" s="2" t="inlineStr">
         <is>
-          <t>Salut - Dental</t>
+          <t>Farmàcies</t>
         </is>
       </c>
       <c r="F478" s="2" t="inlineStr">
@@ -32956,48 +33056,56 @@
       </c>
       <c r="G478" s="2" t="inlineStr">
         <is>
-          <t>Salut - Dental</t>
+          <t>Farmàcies</t>
         </is>
       </c>
       <c r="H478" s="2" t="inlineStr">
         <is>
-          <t>41.5485</t>
+          <t>41.538</t>
         </is>
       </c>
       <c r="I478" s="2" t="inlineStr">
         <is>
-          <t>2.109</t>
-        </is>
-      </c>
-      <c r="J478" s="2" t="inlineStr">
-        <is>
-          <t>medicdentalsabadell.com</t>
-        </is>
-      </c>
+          <t>2.114</t>
+        </is>
+      </c>
+      <c r="J478" s="2" t="inlineStr"/>
       <c r="K478" s="2" t="inlineStr"/>
       <c r="L478" s="2" t="inlineStr"/>
       <c r="M478" s="2" t="inlineStr">
         <is>
-          <t>WebSearch_2026</t>
+          <t>farmacias_2026</t>
         </is>
       </c>
       <c r="N478" s="2" t="inlineStr"/>
       <c r="O478" s="2" t="inlineStr"/>
-      <c r="P478" s="2" t="inlineStr"/>
+      <c r="P478" s="2" t="inlineStr">
+        <is>
+          <t>Carrer de Sol i Padrís 114</t>
+        </is>
+      </c>
       <c r="Q478" s="2" t="inlineStr"/>
     </row>
     <row r="479">
       <c r="A479" s="3" t="inlineStr"/>
-      <c r="B479" s="3" t="inlineStr"/>
-      <c r="C479" s="3" t="inlineStr"/>
+      <c r="B479" s="3" t="inlineStr">
+        <is>
+          <t>Carrer de Sant Cugat</t>
+        </is>
+      </c>
+      <c r="C479" s="3" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
       <c r="D479" s="3" t="inlineStr">
         <is>
-          <t>Inidental Sabadell</t>
+          <t>Farmàcia A. Mercè Sorà</t>
         </is>
       </c>
       <c r="E479" s="3" t="inlineStr">
         <is>
-          <t>Salut - Dental</t>
+          <t>Farmàcies</t>
         </is>
       </c>
       <c r="F479" s="3" t="inlineStr">
@@ -33007,7 +33115,7 @@
       </c>
       <c r="G479" s="3" t="inlineStr">
         <is>
-          <t>Salut - Dental</t>
+          <t>Farmàcies</t>
         </is>
       </c>
       <c r="H479" s="3" t="inlineStr">
@@ -33020,35 +33128,43 @@
           <t>2.109</t>
         </is>
       </c>
-      <c r="J479" s="3" t="inlineStr">
-        <is>
-          <t>inidental.com</t>
-        </is>
-      </c>
+      <c r="J479" s="3" t="inlineStr"/>
       <c r="K479" s="3" t="inlineStr"/>
       <c r="L479" s="3" t="inlineStr"/>
       <c r="M479" s="3" t="inlineStr">
         <is>
-          <t>WebSearch_2026</t>
+          <t>farmacias_2026</t>
         </is>
       </c>
       <c r="N479" s="3" t="inlineStr"/>
       <c r="O479" s="3" t="inlineStr"/>
-      <c r="P479" s="3" t="inlineStr"/>
+      <c r="P479" s="3" t="inlineStr">
+        <is>
+          <t>Carrer de Sant Cugat 95</t>
+        </is>
+      </c>
       <c r="Q479" s="3" t="inlineStr"/>
     </row>
     <row r="480">
       <c r="A480" s="2" t="inlineStr"/>
-      <c r="B480" s="2" t="inlineStr"/>
-      <c r="C480" s="2" t="inlineStr"/>
+      <c r="B480" s="2" t="inlineStr">
+        <is>
+          <t>Carrer de Plini el Vell</t>
+        </is>
+      </c>
+      <c r="C480" s="2" t="inlineStr">
+        <is>
+          <t>1-5</t>
+        </is>
+      </c>
       <c r="D480" s="2" t="inlineStr">
         <is>
-          <t>Centro Médico del Vallès, S.L.</t>
+          <t>Farmàcia J. Herrero Torres</t>
         </is>
       </c>
       <c r="E480" s="2" t="inlineStr">
         <is>
-          <t>Salut - Medicina</t>
+          <t>Farmàcies</t>
         </is>
       </c>
       <c r="F480" s="2" t="inlineStr">
@@ -33058,17 +33174,17 @@
       </c>
       <c r="G480" s="2" t="inlineStr">
         <is>
-          <t>Salut - Medicina</t>
+          <t>Farmàcies</t>
         </is>
       </c>
       <c r="H480" s="2" t="inlineStr">
         <is>
-          <t>41.5485</t>
+          <t>41.553</t>
         </is>
       </c>
       <c r="I480" s="2" t="inlineStr">
         <is>
-          <t>2.109</t>
+          <t>2.0845</t>
         </is>
       </c>
       <c r="J480" s="2" t="inlineStr"/>
@@ -33076,26 +33192,38 @@
       <c r="L480" s="2" t="inlineStr"/>
       <c r="M480" s="2" t="inlineStr">
         <is>
-          <t>WebSearch_2026</t>
+          <t>farmacias_2026</t>
         </is>
       </c>
       <c r="N480" s="2" t="inlineStr"/>
       <c r="O480" s="2" t="inlineStr"/>
-      <c r="P480" s="2" t="inlineStr"/>
+      <c r="P480" s="2" t="inlineStr">
+        <is>
+          <t>Carrer de Plini el Vell 1-5</t>
+        </is>
+      </c>
       <c r="Q480" s="2" t="inlineStr"/>
     </row>
     <row r="481">
       <c r="A481" s="3" t="inlineStr"/>
-      <c r="B481" s="3" t="inlineStr"/>
-      <c r="C481" s="3" t="inlineStr"/>
+      <c r="B481" s="3" t="inlineStr">
+        <is>
+          <t>Carretera de Terrassa</t>
+        </is>
+      </c>
+      <c r="C481" s="3" t="inlineStr">
+        <is>
+          <t>377</t>
+        </is>
+      </c>
       <c r="D481" s="3" t="inlineStr">
         <is>
-          <t>NAEKO S.L.</t>
+          <t>Farmàcia Rosa Maria Carrera Grañó</t>
         </is>
       </c>
       <c r="E481" s="3" t="inlineStr">
         <is>
-          <t>Salut - Medicina</t>
+          <t>Farmàcies</t>
         </is>
       </c>
       <c r="F481" s="3" t="inlineStr">
@@ -33105,17 +33233,17 @@
       </c>
       <c r="G481" s="3" t="inlineStr">
         <is>
-          <t>Salut - Medicina</t>
+          <t>Farmàcies</t>
         </is>
       </c>
       <c r="H481" s="3" t="inlineStr">
         <is>
-          <t>41.5485</t>
+          <t>41.553</t>
         </is>
       </c>
       <c r="I481" s="3" t="inlineStr">
         <is>
-          <t>2.109</t>
+          <t>2.0875</t>
         </is>
       </c>
       <c r="J481" s="3" t="inlineStr"/>
@@ -33123,26 +33251,38 @@
       <c r="L481" s="3" t="inlineStr"/>
       <c r="M481" s="3" t="inlineStr">
         <is>
-          <t>WebSearch_2026</t>
+          <t>farmacias_2026</t>
         </is>
       </c>
       <c r="N481" s="3" t="inlineStr"/>
       <c r="O481" s="3" t="inlineStr"/>
-      <c r="P481" s="3" t="inlineStr"/>
+      <c r="P481" s="3" t="inlineStr">
+        <is>
+          <t>Carretera de Terrassa 377</t>
+        </is>
+      </c>
       <c r="Q481" s="3" t="inlineStr"/>
     </row>
     <row r="482">
       <c r="A482" s="2" t="inlineStr"/>
-      <c r="B482" s="2" t="inlineStr"/>
-      <c r="C482" s="2" t="inlineStr"/>
+      <c r="B482" s="2" t="inlineStr">
+        <is>
+          <t>Avinguda de Concòrdia</t>
+        </is>
+      </c>
+      <c r="C482" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="D482" s="2" t="inlineStr">
         <is>
-          <t>Trauma Salut</t>
+          <t>Farmàcia J. Garrell Roselló</t>
         </is>
       </c>
       <c r="E482" s="2" t="inlineStr">
         <is>
-          <t>Salut - Medicina</t>
+          <t>Farmàcies</t>
         </is>
       </c>
       <c r="F482" s="2" t="inlineStr">
@@ -33152,17 +33292,17 @@
       </c>
       <c r="G482" s="2" t="inlineStr">
         <is>
-          <t>Salut - Medicina</t>
+          <t>Farmàcies</t>
         </is>
       </c>
       <c r="H482" s="2" t="inlineStr">
         <is>
-          <t>41.5485</t>
+          <t>41.553</t>
         </is>
       </c>
       <c r="I482" s="2" t="inlineStr">
         <is>
-          <t>2.109</t>
+          <t>2.0845</t>
         </is>
       </c>
       <c r="J482" s="2" t="inlineStr"/>
@@ -33170,16 +33310,5879 @@
       <c r="L482" s="2" t="inlineStr"/>
       <c r="M482" s="2" t="inlineStr">
         <is>
-          <t>WebSearch_2026</t>
+          <t>farmacias_2026</t>
         </is>
       </c>
       <c r="N482" s="2" t="inlineStr"/>
       <c r="O482" s="2" t="inlineStr"/>
-      <c r="P482" s="2" t="inlineStr"/>
+      <c r="P482" s="2" t="inlineStr">
+        <is>
+          <t>Avinguda de Concòrdia 48</t>
+        </is>
+      </c>
       <c r="Q482" s="2" t="inlineStr"/>
     </row>
+    <row r="483">
+      <c r="A483" s="3" t="inlineStr"/>
+      <c r="B483" s="3" t="inlineStr">
+        <is>
+          <t>Ronda Ponent</t>
+        </is>
+      </c>
+      <c r="C483" s="3" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="D483" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcia RD Ponent 173</t>
+        </is>
+      </c>
+      <c r="E483" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="F483" s="3" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G483" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="H483" s="3" t="inlineStr">
+        <is>
+          <t>41.553</t>
+        </is>
+      </c>
+      <c r="I483" s="3" t="inlineStr">
+        <is>
+          <t>2.0845</t>
+        </is>
+      </c>
+      <c r="J483" s="3" t="inlineStr"/>
+      <c r="K483" s="3" t="inlineStr"/>
+      <c r="L483" s="3" t="inlineStr"/>
+      <c r="M483" s="3" t="inlineStr">
+        <is>
+          <t>farmacias_2026</t>
+        </is>
+      </c>
+      <c r="N483" s="3" t="inlineStr"/>
+      <c r="O483" s="3" t="inlineStr"/>
+      <c r="P483" s="3" t="inlineStr">
+        <is>
+          <t>Ronda Ponent 173</t>
+        </is>
+      </c>
+      <c r="Q483" s="3" t="inlineStr"/>
+    </row>
+    <row r="484">
+      <c r="A484" s="2" t="inlineStr"/>
+      <c r="B484" s="2" t="inlineStr">
+        <is>
+          <t>Antoni Maura</t>
+        </is>
+      </c>
+      <c r="C484" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D484" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcia J. Fontanet Soley</t>
+        </is>
+      </c>
+      <c r="E484" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="F484" s="2" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G484" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="H484" s="2" t="inlineStr">
+        <is>
+          <t>41.5395</t>
+        </is>
+      </c>
+      <c r="I484" s="2" t="inlineStr">
+        <is>
+          <t>2.1095</t>
+        </is>
+      </c>
+      <c r="J484" s="2" t="inlineStr"/>
+      <c r="K484" s="2" t="inlineStr"/>
+      <c r="L484" s="2" t="inlineStr"/>
+      <c r="M484" s="2" t="inlineStr">
+        <is>
+          <t>farmacias_2026</t>
+        </is>
+      </c>
+      <c r="N484" s="2" t="inlineStr"/>
+      <c r="O484" s="2" t="inlineStr"/>
+      <c r="P484" s="2" t="inlineStr">
+        <is>
+          <t>Antoni Maura 52</t>
+        </is>
+      </c>
+      <c r="Q484" s="2" t="inlineStr"/>
+    </row>
+    <row r="485">
+      <c r="A485" s="3" t="inlineStr"/>
+      <c r="B485" s="3" t="inlineStr">
+        <is>
+          <t>Carrer de Borràs</t>
+        </is>
+      </c>
+      <c r="C485" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D485" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcia CL Borràs 8</t>
+        </is>
+      </c>
+      <c r="E485" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="F485" s="3" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G485" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="H485" s="3" t="inlineStr">
+        <is>
+          <t>41.5605</t>
+        </is>
+      </c>
+      <c r="I485" s="3" t="inlineStr">
+        <is>
+          <t>2.1025</t>
+        </is>
+      </c>
+      <c r="J485" s="3" t="inlineStr"/>
+      <c r="K485" s="3" t="inlineStr"/>
+      <c r="L485" s="3" t="inlineStr"/>
+      <c r="M485" s="3" t="inlineStr">
+        <is>
+          <t>farmacias_2026</t>
+        </is>
+      </c>
+      <c r="N485" s="3" t="inlineStr"/>
+      <c r="O485" s="3" t="inlineStr"/>
+      <c r="P485" s="3" t="inlineStr">
+        <is>
+          <t>Carrer de Borràs 8</t>
+        </is>
+      </c>
+      <c r="Q485" s="3" t="inlineStr"/>
+    </row>
+    <row r="486">
+      <c r="A486" s="2" t="inlineStr"/>
+      <c r="B486" s="2" t="inlineStr">
+        <is>
+          <t>Sallarès i Pla</t>
+        </is>
+      </c>
+      <c r="C486" s="2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="D486" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcia M. Garriga Majó</t>
+        </is>
+      </c>
+      <c r="E486" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="F486" s="2" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G486" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="H486" s="2" t="inlineStr">
+        <is>
+          <t>41.5475</t>
+        </is>
+      </c>
+      <c r="I486" s="2" t="inlineStr">
+        <is>
+          <t>2.107</t>
+        </is>
+      </c>
+      <c r="J486" s="2" t="inlineStr"/>
+      <c r="K486" s="2" t="inlineStr"/>
+      <c r="L486" s="2" t="inlineStr"/>
+      <c r="M486" s="2" t="inlineStr">
+        <is>
+          <t>farmacias_2026</t>
+        </is>
+      </c>
+      <c r="N486" s="2" t="inlineStr"/>
+      <c r="O486" s="2" t="inlineStr"/>
+      <c r="P486" s="2" t="inlineStr">
+        <is>
+          <t>Sallarès i Pla 140</t>
+        </is>
+      </c>
+      <c r="Q486" s="2" t="inlineStr"/>
+    </row>
+    <row r="487">
+      <c r="A487" s="3" t="inlineStr"/>
+      <c r="B487" s="3" t="inlineStr">
+        <is>
+          <t>Portal de la Floresta</t>
+        </is>
+      </c>
+      <c r="C487" s="3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D487" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcia Portal de la Floresta</t>
+        </is>
+      </c>
+      <c r="E487" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="F487" s="3" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G487" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="H487" s="3" t="inlineStr">
+        <is>
+          <t>41.564</t>
+        </is>
+      </c>
+      <c r="I487" s="3" t="inlineStr">
+        <is>
+          <t>2.0905</t>
+        </is>
+      </c>
+      <c r="J487" s="3" t="inlineStr"/>
+      <c r="K487" s="3" t="inlineStr"/>
+      <c r="L487" s="3" t="inlineStr"/>
+      <c r="M487" s="3" t="inlineStr">
+        <is>
+          <t>farmacias_2026</t>
+        </is>
+      </c>
+      <c r="N487" s="3" t="inlineStr"/>
+      <c r="O487" s="3" t="inlineStr"/>
+      <c r="P487" s="3" t="inlineStr">
+        <is>
+          <t>Portal de la Floresta 25</t>
+        </is>
+      </c>
+      <c r="Q487" s="3" t="inlineStr"/>
+    </row>
+    <row r="488">
+      <c r="A488" s="2" t="inlineStr"/>
+      <c r="B488" s="2" t="inlineStr">
+        <is>
+          <t>Avinguda de Reis Catòlics</t>
+        </is>
+      </c>
+      <c r="C488" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D488" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcia C. Ferrer San José</t>
+        </is>
+      </c>
+      <c r="E488" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="F488" s="2" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G488" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="H488" s="2" t="inlineStr">
+        <is>
+          <t>41.5395</t>
+        </is>
+      </c>
+      <c r="I488" s="2" t="inlineStr">
+        <is>
+          <t>2.1095</t>
+        </is>
+      </c>
+      <c r="J488" s="2" t="inlineStr"/>
+      <c r="K488" s="2" t="inlineStr"/>
+      <c r="L488" s="2" t="inlineStr"/>
+      <c r="M488" s="2" t="inlineStr">
+        <is>
+          <t>farmacias_2026</t>
+        </is>
+      </c>
+      <c r="N488" s="2" t="inlineStr"/>
+      <c r="O488" s="2" t="inlineStr"/>
+      <c r="P488" s="2" t="inlineStr">
+        <is>
+          <t>Avinguda de Reis Catòlics 39</t>
+        </is>
+      </c>
+      <c r="Q488" s="2" t="inlineStr"/>
+    </row>
+    <row r="489">
+      <c r="A489" s="3" t="inlineStr"/>
+      <c r="B489" s="3" t="inlineStr">
+        <is>
+          <t>Lusitania Bl-2 L-49</t>
+        </is>
+      </c>
+      <c r="C489" s="3" t="inlineStr"/>
+      <c r="D489" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcia Lusitania</t>
+        </is>
+      </c>
+      <c r="E489" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="F489" s="3" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G489" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="H489" s="3" t="inlineStr">
+        <is>
+          <t>41.553</t>
+        </is>
+      </c>
+      <c r="I489" s="3" t="inlineStr">
+        <is>
+          <t>2.0845</t>
+        </is>
+      </c>
+      <c r="J489" s="3" t="inlineStr"/>
+      <c r="K489" s="3" t="inlineStr"/>
+      <c r="L489" s="3" t="inlineStr"/>
+      <c r="M489" s="3" t="inlineStr">
+        <is>
+          <t>farmacias_2026</t>
+        </is>
+      </c>
+      <c r="N489" s="3" t="inlineStr"/>
+      <c r="O489" s="3" t="inlineStr"/>
+      <c r="P489" s="3" t="inlineStr">
+        <is>
+          <t>Lusitania Bl-2 L-49</t>
+        </is>
+      </c>
+      <c r="Q489" s="3" t="inlineStr"/>
+    </row>
+    <row r="490">
+      <c r="A490" s="2" t="inlineStr"/>
+      <c r="B490" s="2" t="inlineStr">
+        <is>
+          <t>Passeig de Plaça Major</t>
+        </is>
+      </c>
+      <c r="C490" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D490" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcia A. Garriga Majó</t>
+        </is>
+      </c>
+      <c r="E490" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="F490" s="2" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G490" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="H490" s="2" t="inlineStr">
+        <is>
+          <t>41.5485</t>
+        </is>
+      </c>
+      <c r="I490" s="2" t="inlineStr">
+        <is>
+          <t>2.109</t>
+        </is>
+      </c>
+      <c r="J490" s="2" t="inlineStr"/>
+      <c r="K490" s="2" t="inlineStr"/>
+      <c r="L490" s="2" t="inlineStr"/>
+      <c r="M490" s="2" t="inlineStr">
+        <is>
+          <t>farmacias_2026</t>
+        </is>
+      </c>
+      <c r="N490" s="2" t="inlineStr"/>
+      <c r="O490" s="2" t="inlineStr"/>
+      <c r="P490" s="2" t="inlineStr">
+        <is>
+          <t>Passeig de Plaça Major 29</t>
+        </is>
+      </c>
+      <c r="Q490" s="2" t="inlineStr"/>
+    </row>
+    <row r="491">
+      <c r="A491" s="3" t="inlineStr"/>
+      <c r="B491" s="3" t="inlineStr">
+        <is>
+          <t>Carretera de Terrassa</t>
+        </is>
+      </c>
+      <c r="C491" s="3" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="D491" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcia O. Gadea Melo</t>
+        </is>
+      </c>
+      <c r="E491" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="F491" s="3" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G491" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="H491" s="3" t="inlineStr">
+        <is>
+          <t>41.553</t>
+        </is>
+      </c>
+      <c r="I491" s="3" t="inlineStr">
+        <is>
+          <t>2.0845</t>
+        </is>
+      </c>
+      <c r="J491" s="3" t="inlineStr"/>
+      <c r="K491" s="3" t="inlineStr"/>
+      <c r="L491" s="3" t="inlineStr"/>
+      <c r="M491" s="3" t="inlineStr">
+        <is>
+          <t>farmacias_2026</t>
+        </is>
+      </c>
+      <c r="N491" s="3" t="inlineStr"/>
+      <c r="O491" s="3" t="inlineStr"/>
+      <c r="P491" s="3" t="inlineStr">
+        <is>
+          <t>Carretera de Terrassa 316</t>
+        </is>
+      </c>
+      <c r="Q491" s="3" t="inlineStr"/>
+    </row>
+    <row r="492">
+      <c r="A492" s="2" t="inlineStr"/>
+      <c r="B492" s="2" t="inlineStr">
+        <is>
+          <t>Avinguda de Polinyà</t>
+        </is>
+      </c>
+      <c r="C492" s="2" t="inlineStr">
+        <is>
+          <t>65 loc-4</t>
+        </is>
+      </c>
+      <c r="D492" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcia G. Grau Saurí</t>
+        </is>
+      </c>
+      <c r="E492" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="F492" s="2" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G492" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="H492" s="2" t="inlineStr">
+        <is>
+          <t>41.5475</t>
+        </is>
+      </c>
+      <c r="I492" s="2" t="inlineStr">
+        <is>
+          <t>2.107</t>
+        </is>
+      </c>
+      <c r="J492" s="2" t="inlineStr"/>
+      <c r="K492" s="2" t="inlineStr"/>
+      <c r="L492" s="2" t="inlineStr"/>
+      <c r="M492" s="2" t="inlineStr">
+        <is>
+          <t>farmacias_2026</t>
+        </is>
+      </c>
+      <c r="N492" s="2" t="inlineStr"/>
+      <c r="O492" s="2" t="inlineStr"/>
+      <c r="P492" s="2" t="inlineStr">
+        <is>
+          <t>Avinguda de Polinyà 65 loc-4</t>
+        </is>
+      </c>
+      <c r="Q492" s="2" t="inlineStr"/>
+    </row>
+    <row r="493">
+      <c r="A493" s="3" t="inlineStr"/>
+      <c r="B493" s="3" t="inlineStr">
+        <is>
+          <t>Sant Antoni M. Claret</t>
+        </is>
+      </c>
+      <c r="C493" s="3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D493" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcia S. Argelaguet Argemí</t>
+        </is>
+      </c>
+      <c r="E493" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="F493" s="3" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G493" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="H493" s="3" t="inlineStr">
+        <is>
+          <t>41.5475</t>
+        </is>
+      </c>
+      <c r="I493" s="3" t="inlineStr">
+        <is>
+          <t>2.107</t>
+        </is>
+      </c>
+      <c r="J493" s="3" t="inlineStr"/>
+      <c r="K493" s="3" t="inlineStr"/>
+      <c r="L493" s="3" t="inlineStr"/>
+      <c r="M493" s="3" t="inlineStr">
+        <is>
+          <t>farmacias_2026</t>
+        </is>
+      </c>
+      <c r="N493" s="3" t="inlineStr"/>
+      <c r="O493" s="3" t="inlineStr"/>
+      <c r="P493" s="3" t="inlineStr">
+        <is>
+          <t>Sant Antoni M. Claret 21</t>
+        </is>
+      </c>
+      <c r="Q493" s="3" t="inlineStr"/>
+    </row>
+    <row r="494">
+      <c r="A494" s="2" t="inlineStr"/>
+      <c r="B494" s="2" t="inlineStr">
+        <is>
+          <t>Carrer de Fernando Poo</t>
+        </is>
+      </c>
+      <c r="C494" s="2" t="inlineStr">
+        <is>
+          <t>31-33</t>
+        </is>
+      </c>
+      <c r="D494" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcia M. Rosell Gras</t>
+        </is>
+      </c>
+      <c r="E494" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="F494" s="2" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G494" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="H494" s="2" t="inlineStr">
+        <is>
+          <t>41.553</t>
+        </is>
+      </c>
+      <c r="I494" s="2" t="inlineStr">
+        <is>
+          <t>2.0875</t>
+        </is>
+      </c>
+      <c r="J494" s="2" t="inlineStr"/>
+      <c r="K494" s="2" t="inlineStr"/>
+      <c r="L494" s="2" t="inlineStr"/>
+      <c r="M494" s="2" t="inlineStr">
+        <is>
+          <t>farmacias_2026</t>
+        </is>
+      </c>
+      <c r="N494" s="2" t="inlineStr"/>
+      <c r="O494" s="2" t="inlineStr"/>
+      <c r="P494" s="2" t="inlineStr">
+        <is>
+          <t>Carrer de Fernando Poo 31-33</t>
+        </is>
+      </c>
+      <c r="Q494" s="2" t="inlineStr"/>
+    </row>
+    <row r="495">
+      <c r="A495" s="3" t="inlineStr"/>
+      <c r="B495" s="3" t="inlineStr">
+        <is>
+          <t>Plaça de de l'Àngel</t>
+        </is>
+      </c>
+      <c r="C495" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D495" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcia M. Gili Segura</t>
+        </is>
+      </c>
+      <c r="E495" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="F495" s="3" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G495" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="H495" s="3" t="inlineStr">
+        <is>
+          <t>41.5475</t>
+        </is>
+      </c>
+      <c r="I495" s="3" t="inlineStr">
+        <is>
+          <t>2.107</t>
+        </is>
+      </c>
+      <c r="J495" s="3" t="inlineStr"/>
+      <c r="K495" s="3" t="inlineStr"/>
+      <c r="L495" s="3" t="inlineStr"/>
+      <c r="M495" s="3" t="inlineStr">
+        <is>
+          <t>farmacias_2026</t>
+        </is>
+      </c>
+      <c r="N495" s="3" t="inlineStr"/>
+      <c r="O495" s="3" t="inlineStr"/>
+      <c r="P495" s="3" t="inlineStr">
+        <is>
+          <t>Plaça de de l'Àngel 12</t>
+        </is>
+      </c>
+      <c r="Q495" s="3" t="inlineStr"/>
+    </row>
+    <row r="496">
+      <c r="A496" s="2" t="inlineStr"/>
+      <c r="B496" s="2" t="inlineStr">
+        <is>
+          <t>Carrer de Viladomat</t>
+        </is>
+      </c>
+      <c r="C496" s="2" t="inlineStr">
+        <is>
+          <t>20-24</t>
+        </is>
+      </c>
+      <c r="D496" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcia A. Mujal Viñals</t>
+        </is>
+      </c>
+      <c r="E496" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="F496" s="2" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G496" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="H496" s="2" t="inlineStr">
+        <is>
+          <t>41.553</t>
+        </is>
+      </c>
+      <c r="I496" s="2" t="inlineStr">
+        <is>
+          <t>2.0875</t>
+        </is>
+      </c>
+      <c r="J496" s="2" t="inlineStr"/>
+      <c r="K496" s="2" t="inlineStr"/>
+      <c r="L496" s="2" t="inlineStr"/>
+      <c r="M496" s="2" t="inlineStr">
+        <is>
+          <t>farmacias_2026</t>
+        </is>
+      </c>
+      <c r="N496" s="2" t="inlineStr"/>
+      <c r="O496" s="2" t="inlineStr"/>
+      <c r="P496" s="2" t="inlineStr">
+        <is>
+          <t>Carrer de Viladomat 20-24</t>
+        </is>
+      </c>
+      <c r="Q496" s="2" t="inlineStr"/>
+    </row>
+    <row r="497">
+      <c r="A497" s="3" t="inlineStr"/>
+      <c r="B497" s="3" t="inlineStr">
+        <is>
+          <t>Via Massagué</t>
+        </is>
+      </c>
+      <c r="C497" s="3" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D497" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcia Via Massagué</t>
+        </is>
+      </c>
+      <c r="E497" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="F497" s="3" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G497" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="H497" s="3" t="inlineStr">
+        <is>
+          <t>41.5475</t>
+        </is>
+      </c>
+      <c r="I497" s="3" t="inlineStr">
+        <is>
+          <t>2.107</t>
+        </is>
+      </c>
+      <c r="J497" s="3" t="inlineStr"/>
+      <c r="K497" s="3" t="inlineStr"/>
+      <c r="L497" s="3" t="inlineStr"/>
+      <c r="M497" s="3" t="inlineStr">
+        <is>
+          <t>farmacias_2026</t>
+        </is>
+      </c>
+      <c r="N497" s="3" t="inlineStr"/>
+      <c r="O497" s="3" t="inlineStr"/>
+      <c r="P497" s="3" t="inlineStr">
+        <is>
+          <t>Via Massagué 40</t>
+        </is>
+      </c>
+      <c r="Q497" s="3" t="inlineStr"/>
+    </row>
+    <row r="498">
+      <c r="A498" s="2" t="inlineStr"/>
+      <c r="B498" s="2" t="inlineStr">
+        <is>
+          <t>Avinguda de Matadepera Can Oriach</t>
+        </is>
+      </c>
+      <c r="C498" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D498" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcia B. Domènech Sagué</t>
+        </is>
+      </c>
+      <c r="E498" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="F498" s="2" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G498" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="H498" s="2" t="inlineStr">
+        <is>
+          <t>41.564</t>
+        </is>
+      </c>
+      <c r="I498" s="2" t="inlineStr">
+        <is>
+          <t>2.0905</t>
+        </is>
+      </c>
+      <c r="J498" s="2" t="inlineStr"/>
+      <c r="K498" s="2" t="inlineStr"/>
+      <c r="L498" s="2" t="inlineStr"/>
+      <c r="M498" s="2" t="inlineStr">
+        <is>
+          <t>farmacias_2026</t>
+        </is>
+      </c>
+      <c r="N498" s="2" t="inlineStr"/>
+      <c r="O498" s="2" t="inlineStr"/>
+      <c r="P498" s="2" t="inlineStr">
+        <is>
+          <t>Avinguda de Matadepera Can Oriach 82</t>
+        </is>
+      </c>
+      <c r="Q498" s="2" t="inlineStr"/>
+    </row>
+    <row r="499">
+      <c r="A499" s="3" t="inlineStr"/>
+      <c r="B499" s="3" t="inlineStr">
+        <is>
+          <t>Avinguda de Barberà</t>
+        </is>
+      </c>
+      <c r="C499" s="3" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="D499" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcia M. Fàbregas Martínez</t>
+        </is>
+      </c>
+      <c r="E499" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="F499" s="3" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G499" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="H499" s="3" t="inlineStr">
+        <is>
+          <t>41.538</t>
+        </is>
+      </c>
+      <c r="I499" s="3" t="inlineStr">
+        <is>
+          <t>2.114</t>
+        </is>
+      </c>
+      <c r="J499" s="3" t="inlineStr"/>
+      <c r="K499" s="3" t="inlineStr"/>
+      <c r="L499" s="3" t="inlineStr"/>
+      <c r="M499" s="3" t="inlineStr">
+        <is>
+          <t>farmacias_2026</t>
+        </is>
+      </c>
+      <c r="N499" s="3" t="inlineStr"/>
+      <c r="O499" s="3" t="inlineStr"/>
+      <c r="P499" s="3" t="inlineStr">
+        <is>
+          <t>Avinguda de Barberà 299</t>
+        </is>
+      </c>
+      <c r="Q499" s="3" t="inlineStr"/>
+    </row>
+    <row r="500">
+      <c r="A500" s="2" t="inlineStr"/>
+      <c r="B500" s="2" t="inlineStr">
+        <is>
+          <t>Cesar Torras</t>
+        </is>
+      </c>
+      <c r="C500" s="2" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D500" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcia Cesar Torras</t>
+        </is>
+      </c>
+      <c r="E500" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="F500" s="2" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G500" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="H500" s="2" t="inlineStr">
+        <is>
+          <t>41.553</t>
+        </is>
+      </c>
+      <c r="I500" s="2" t="inlineStr">
+        <is>
+          <t>2.0875</t>
+        </is>
+      </c>
+      <c r="J500" s="2" t="inlineStr"/>
+      <c r="K500" s="2" t="inlineStr"/>
+      <c r="L500" s="2" t="inlineStr"/>
+      <c r="M500" s="2" t="inlineStr">
+        <is>
+          <t>farmacias_2026</t>
+        </is>
+      </c>
+      <c r="N500" s="2" t="inlineStr"/>
+      <c r="O500" s="2" t="inlineStr"/>
+      <c r="P500" s="2" t="inlineStr">
+        <is>
+          <t>Cesar Torras 132</t>
+        </is>
+      </c>
+      <c r="Q500" s="2" t="inlineStr"/>
+    </row>
+    <row r="501">
+      <c r="A501" s="3" t="inlineStr"/>
+      <c r="B501" s="3" t="inlineStr">
+        <is>
+          <t>Llanera</t>
+        </is>
+      </c>
+      <c r="C501" s="3" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D501" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcia M. Bonet Ortiz</t>
+        </is>
+      </c>
+      <c r="E501" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="F501" s="3" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G501" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="H501" s="3" t="inlineStr">
+        <is>
+          <t>41.564</t>
+        </is>
+      </c>
+      <c r="I501" s="3" t="inlineStr">
+        <is>
+          <t>2.0905</t>
+        </is>
+      </c>
+      <c r="J501" s="3" t="inlineStr"/>
+      <c r="K501" s="3" t="inlineStr"/>
+      <c r="L501" s="3" t="inlineStr"/>
+      <c r="M501" s="3" t="inlineStr">
+        <is>
+          <t>farmacias_2026</t>
+        </is>
+      </c>
+      <c r="N501" s="3" t="inlineStr"/>
+      <c r="O501" s="3" t="inlineStr"/>
+      <c r="P501" s="3" t="inlineStr">
+        <is>
+          <t>Llanera 93</t>
+        </is>
+      </c>
+      <c r="Q501" s="3" t="inlineStr"/>
+    </row>
+    <row r="502">
+      <c r="A502" s="2" t="inlineStr"/>
+      <c r="B502" s="2" t="inlineStr">
+        <is>
+          <t>Carme</t>
+        </is>
+      </c>
+      <c r="C502" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D502" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcia M. Bagán Tapiolas</t>
+        </is>
+      </c>
+      <c r="E502" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="F502" s="2" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G502" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="H502" s="2" t="inlineStr">
+        <is>
+          <t>41.5475</t>
+        </is>
+      </c>
+      <c r="I502" s="2" t="inlineStr">
+        <is>
+          <t>2.107</t>
+        </is>
+      </c>
+      <c r="J502" s="2" t="inlineStr"/>
+      <c r="K502" s="2" t="inlineStr"/>
+      <c r="L502" s="2" t="inlineStr"/>
+      <c r="M502" s="2" t="inlineStr">
+        <is>
+          <t>farmacias_2026</t>
+        </is>
+      </c>
+      <c r="N502" s="2" t="inlineStr"/>
+      <c r="O502" s="2" t="inlineStr"/>
+      <c r="P502" s="2" t="inlineStr">
+        <is>
+          <t>Carme 10</t>
+        </is>
+      </c>
+      <c r="Q502" s="2" t="inlineStr"/>
+    </row>
+    <row r="503">
+      <c r="A503" s="3" t="inlineStr"/>
+      <c r="B503" s="3" t="inlineStr">
+        <is>
+          <t>Carrer de Ramon Jové</t>
+        </is>
+      </c>
+      <c r="C503" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D503" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcia A. Grau Martí</t>
+        </is>
+      </c>
+      <c r="E503" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="F503" s="3" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G503" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="H503" s="3" t="inlineStr">
+        <is>
+          <t>41.5605</t>
+        </is>
+      </c>
+      <c r="I503" s="3" t="inlineStr">
+        <is>
+          <t>2.1025</t>
+        </is>
+      </c>
+      <c r="J503" s="3" t="inlineStr"/>
+      <c r="K503" s="3" t="inlineStr"/>
+      <c r="L503" s="3" t="inlineStr"/>
+      <c r="M503" s="3" t="inlineStr">
+        <is>
+          <t>farmacias_2026</t>
+        </is>
+      </c>
+      <c r="N503" s="3" t="inlineStr"/>
+      <c r="O503" s="3" t="inlineStr"/>
+      <c r="P503" s="3" t="inlineStr">
+        <is>
+          <t>Carrer de Ramon Jové 2</t>
+        </is>
+      </c>
+      <c r="Q503" s="3" t="inlineStr"/>
+    </row>
+    <row r="504">
+      <c r="A504" s="2" t="inlineStr"/>
+      <c r="B504" s="2" t="inlineStr">
+        <is>
+          <t>Avinguda de Onze de Setembre</t>
+        </is>
+      </c>
+      <c r="C504" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D504" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcia AV Onze de Setembre 61</t>
+        </is>
+      </c>
+      <c r="E504" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="F504" s="2" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G504" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="H504" s="2" t="inlineStr">
+        <is>
+          <t>41.5605</t>
+        </is>
+      </c>
+      <c r="I504" s="2" t="inlineStr">
+        <is>
+          <t>2.1025</t>
+        </is>
+      </c>
+      <c r="J504" s="2" t="inlineStr"/>
+      <c r="K504" s="2" t="inlineStr"/>
+      <c r="L504" s="2" t="inlineStr"/>
+      <c r="M504" s="2" t="inlineStr">
+        <is>
+          <t>farmacias_2026</t>
+        </is>
+      </c>
+      <c r="N504" s="2" t="inlineStr"/>
+      <c r="O504" s="2" t="inlineStr"/>
+      <c r="P504" s="2" t="inlineStr">
+        <is>
+          <t>Avinguda de Onze de Setembre 61</t>
+        </is>
+      </c>
+      <c r="Q504" s="2" t="inlineStr"/>
+    </row>
+    <row r="505">
+      <c r="A505" s="3" t="inlineStr"/>
+      <c r="B505" s="3" t="inlineStr">
+        <is>
+          <t>Avinguda de Barberà</t>
+        </is>
+      </c>
+      <c r="C505" s="3" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D505" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcia M. Mias Poblet</t>
+        </is>
+      </c>
+      <c r="E505" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="F505" s="3" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G505" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="H505" s="3" t="inlineStr">
+        <is>
+          <t>41.538</t>
+        </is>
+      </c>
+      <c r="I505" s="3" t="inlineStr">
+        <is>
+          <t>2.114</t>
+        </is>
+      </c>
+      <c r="J505" s="3" t="inlineStr"/>
+      <c r="K505" s="3" t="inlineStr"/>
+      <c r="L505" s="3" t="inlineStr"/>
+      <c r="M505" s="3" t="inlineStr">
+        <is>
+          <t>farmacias_2026</t>
+        </is>
+      </c>
+      <c r="N505" s="3" t="inlineStr"/>
+      <c r="O505" s="3" t="inlineStr"/>
+      <c r="P505" s="3" t="inlineStr">
+        <is>
+          <t>Avinguda de Barberà 48</t>
+        </is>
+      </c>
+      <c r="Q505" s="3" t="inlineStr"/>
+    </row>
+    <row r="506">
+      <c r="A506" s="2" t="inlineStr"/>
+      <c r="B506" s="2" t="inlineStr">
+        <is>
+          <t>Rambla Sabadell</t>
+        </is>
+      </c>
+      <c r="C506" s="2" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D506" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcia M. Morales Guarch</t>
+        </is>
+      </c>
+      <c r="E506" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="F506" s="2" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G506" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="H506" s="2" t="inlineStr">
+        <is>
+          <t>41.5475</t>
+        </is>
+      </c>
+      <c r="I506" s="2" t="inlineStr">
+        <is>
+          <t>2.107</t>
+        </is>
+      </c>
+      <c r="J506" s="2" t="inlineStr"/>
+      <c r="K506" s="2" t="inlineStr"/>
+      <c r="L506" s="2" t="inlineStr"/>
+      <c r="M506" s="2" t="inlineStr">
+        <is>
+          <t>farmacias_2026</t>
+        </is>
+      </c>
+      <c r="N506" s="2" t="inlineStr"/>
+      <c r="O506" s="2" t="inlineStr"/>
+      <c r="P506" s="2" t="inlineStr">
+        <is>
+          <t>Rambla Sabadell 165</t>
+        </is>
+      </c>
+      <c r="Q506" s="2" t="inlineStr"/>
+    </row>
+    <row r="507">
+      <c r="A507" s="3" t="inlineStr"/>
+      <c r="B507" s="3" t="inlineStr">
+        <is>
+          <t>Rambla Sabadell</t>
+        </is>
+      </c>
+      <c r="C507" s="3" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D507" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcia J. Vinyes Sant</t>
+        </is>
+      </c>
+      <c r="E507" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="F507" s="3" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G507" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="H507" s="3" t="inlineStr">
+        <is>
+          <t>41.5475</t>
+        </is>
+      </c>
+      <c r="I507" s="3" t="inlineStr">
+        <is>
+          <t>2.107</t>
+        </is>
+      </c>
+      <c r="J507" s="3" t="inlineStr"/>
+      <c r="K507" s="3" t="inlineStr"/>
+      <c r="L507" s="3" t="inlineStr"/>
+      <c r="M507" s="3" t="inlineStr">
+        <is>
+          <t>farmacias_2026</t>
+        </is>
+      </c>
+      <c r="N507" s="3" t="inlineStr"/>
+      <c r="O507" s="3" t="inlineStr"/>
+      <c r="P507" s="3" t="inlineStr">
+        <is>
+          <t>Rambla Sabadell 235</t>
+        </is>
+      </c>
+      <c r="Q507" s="3" t="inlineStr"/>
+    </row>
+    <row r="508">
+      <c r="A508" s="2" t="inlineStr"/>
+      <c r="B508" s="2" t="inlineStr">
+        <is>
+          <t>Carrer de Sant Cugat</t>
+        </is>
+      </c>
+      <c r="C508" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D508" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcia I. Pons Samaranch</t>
+        </is>
+      </c>
+      <c r="E508" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="F508" s="2" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G508" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="H508" s="2" t="inlineStr">
+        <is>
+          <t>41.5485</t>
+        </is>
+      </c>
+      <c r="I508" s="2" t="inlineStr">
+        <is>
+          <t>2.109</t>
+        </is>
+      </c>
+      <c r="J508" s="2" t="inlineStr"/>
+      <c r="K508" s="2" t="inlineStr"/>
+      <c r="L508" s="2" t="inlineStr"/>
+      <c r="M508" s="2" t="inlineStr">
+        <is>
+          <t>farmacias_2026</t>
+        </is>
+      </c>
+      <c r="N508" s="2" t="inlineStr"/>
+      <c r="O508" s="2" t="inlineStr"/>
+      <c r="P508" s="2" t="inlineStr">
+        <is>
+          <t>Carrer de Sant Cugat 2</t>
+        </is>
+      </c>
+      <c r="Q508" s="2" t="inlineStr"/>
+    </row>
+    <row r="509">
+      <c r="A509" s="3" t="inlineStr"/>
+      <c r="B509" s="3" t="inlineStr">
+        <is>
+          <t>Via Alexandra</t>
+        </is>
+      </c>
+      <c r="C509" s="3" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D509" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcia L. Puig Camarero</t>
+        </is>
+      </c>
+      <c r="E509" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="F509" s="3" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G509" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="H509" s="3" t="inlineStr">
+        <is>
+          <t>41.553</t>
+        </is>
+      </c>
+      <c r="I509" s="3" t="inlineStr">
+        <is>
+          <t>2.0845</t>
+        </is>
+      </c>
+      <c r="J509" s="3" t="inlineStr"/>
+      <c r="K509" s="3" t="inlineStr"/>
+      <c r="L509" s="3" t="inlineStr"/>
+      <c r="M509" s="3" t="inlineStr">
+        <is>
+          <t>farmacias_2026</t>
+        </is>
+      </c>
+      <c r="N509" s="3" t="inlineStr"/>
+      <c r="O509" s="3" t="inlineStr"/>
+      <c r="P509" s="3" t="inlineStr">
+        <is>
+          <t>Via Alexandra 37</t>
+        </is>
+      </c>
+      <c r="Q509" s="3" t="inlineStr"/>
+    </row>
+    <row r="510">
+      <c r="A510" s="2" t="inlineStr"/>
+      <c r="B510" s="2" t="inlineStr">
+        <is>
+          <t>Brutau</t>
+        </is>
+      </c>
+      <c r="C510" s="2" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D510" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcia M. Montserrat Marco</t>
+        </is>
+      </c>
+      <c r="E510" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="F510" s="2" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G510" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="H510" s="2" t="inlineStr">
+        <is>
+          <t>41.538</t>
+        </is>
+      </c>
+      <c r="I510" s="2" t="inlineStr">
+        <is>
+          <t>2.114</t>
+        </is>
+      </c>
+      <c r="J510" s="2" t="inlineStr"/>
+      <c r="K510" s="2" t="inlineStr"/>
+      <c r="L510" s="2" t="inlineStr"/>
+      <c r="M510" s="2" t="inlineStr">
+        <is>
+          <t>farmacias_2026</t>
+        </is>
+      </c>
+      <c r="N510" s="2" t="inlineStr"/>
+      <c r="O510" s="2" t="inlineStr"/>
+      <c r="P510" s="2" t="inlineStr">
+        <is>
+          <t>Brutau 187</t>
+        </is>
+      </c>
+      <c r="Q510" s="2" t="inlineStr"/>
+    </row>
+    <row r="511">
+      <c r="A511" s="3" t="inlineStr"/>
+      <c r="B511" s="3" t="inlineStr">
+        <is>
+          <t>Plaça de Creu de Barberà</t>
+        </is>
+      </c>
+      <c r="C511" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D511" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcia J. Baradad Solana</t>
+        </is>
+      </c>
+      <c r="E511" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="F511" s="3" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G511" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="H511" s="3" t="inlineStr">
+        <is>
+          <t>41.5395</t>
+        </is>
+      </c>
+      <c r="I511" s="3" t="inlineStr">
+        <is>
+          <t>2.1095</t>
+        </is>
+      </c>
+      <c r="J511" s="3" t="inlineStr"/>
+      <c r="K511" s="3" t="inlineStr"/>
+      <c r="L511" s="3" t="inlineStr"/>
+      <c r="M511" s="3" t="inlineStr">
+        <is>
+          <t>farmacias_2026</t>
+        </is>
+      </c>
+      <c r="N511" s="3" t="inlineStr"/>
+      <c r="O511" s="3" t="inlineStr"/>
+      <c r="P511" s="3" t="inlineStr">
+        <is>
+          <t>Plaça de Creu de Barberà 8</t>
+        </is>
+      </c>
+      <c r="Q511" s="3" t="inlineStr"/>
+    </row>
+    <row r="512">
+      <c r="A512" s="2" t="inlineStr"/>
+      <c r="B512" s="2" t="inlineStr">
+        <is>
+          <t>Pintor Vila Cinca</t>
+        </is>
+      </c>
+      <c r="C512" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D512" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcia P. Escarrà Caldès</t>
+        </is>
+      </c>
+      <c r="E512" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="F512" s="2" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G512" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="H512" s="2" t="inlineStr">
+        <is>
+          <t>41.5605</t>
+        </is>
+      </c>
+      <c r="I512" s="2" t="inlineStr">
+        <is>
+          <t>2.1025</t>
+        </is>
+      </c>
+      <c r="J512" s="2" t="inlineStr"/>
+      <c r="K512" s="2" t="inlineStr"/>
+      <c r="L512" s="2" t="inlineStr"/>
+      <c r="M512" s="2" t="inlineStr">
+        <is>
+          <t>farmacias_2026</t>
+        </is>
+      </c>
+      <c r="N512" s="2" t="inlineStr"/>
+      <c r="O512" s="2" t="inlineStr"/>
+      <c r="P512" s="2" t="inlineStr">
+        <is>
+          <t>Pintor Vila Cinca 89</t>
+        </is>
+      </c>
+      <c r="Q512" s="2" t="inlineStr"/>
+    </row>
+    <row r="513">
+      <c r="A513" s="3" t="inlineStr"/>
+      <c r="B513" s="3" t="inlineStr">
+        <is>
+          <t>Plaça de Còrdova</t>
+        </is>
+      </c>
+      <c r="C513" s="3" t="inlineStr">
+        <is>
+          <t>14-15</t>
+        </is>
+      </c>
+      <c r="D513" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcia M. Franco García</t>
+        </is>
+      </c>
+      <c r="E513" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="F513" s="3" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G513" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="H513" s="3" t="inlineStr">
+        <is>
+          <t>41.553</t>
+        </is>
+      </c>
+      <c r="I513" s="3" t="inlineStr">
+        <is>
+          <t>2.0845</t>
+        </is>
+      </c>
+      <c r="J513" s="3" t="inlineStr"/>
+      <c r="K513" s="3" t="inlineStr"/>
+      <c r="L513" s="3" t="inlineStr"/>
+      <c r="M513" s="3" t="inlineStr">
+        <is>
+          <t>farmacias_2026</t>
+        </is>
+      </c>
+      <c r="N513" s="3" t="inlineStr"/>
+      <c r="O513" s="3" t="inlineStr"/>
+      <c r="P513" s="3" t="inlineStr">
+        <is>
+          <t>Plaça de Còrdova 14-15</t>
+        </is>
+      </c>
+      <c r="Q513" s="3" t="inlineStr"/>
+    </row>
+    <row r="514">
+      <c r="A514" s="2" t="inlineStr"/>
+      <c r="B514" s="2" t="inlineStr">
+        <is>
+          <t>Carretera de Prats de Lluçanès</t>
+        </is>
+      </c>
+      <c r="C514" s="2" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D514" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcia CR Prats de Lluçanès 208</t>
+        </is>
+      </c>
+      <c r="E514" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="F514" s="2" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G514" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="H514" s="2" t="inlineStr">
+        <is>
+          <t>41.5605</t>
+        </is>
+      </c>
+      <c r="I514" s="2" t="inlineStr">
+        <is>
+          <t>2.1025</t>
+        </is>
+      </c>
+      <c r="J514" s="2" t="inlineStr"/>
+      <c r="K514" s="2" t="inlineStr"/>
+      <c r="L514" s="2" t="inlineStr"/>
+      <c r="M514" s="2" t="inlineStr">
+        <is>
+          <t>farmacias_2026</t>
+        </is>
+      </c>
+      <c r="N514" s="2" t="inlineStr"/>
+      <c r="O514" s="2" t="inlineStr"/>
+      <c r="P514" s="2" t="inlineStr">
+        <is>
+          <t>Carretera de Prats de Lluçanès 208</t>
+        </is>
+      </c>
+      <c r="Q514" s="2" t="inlineStr"/>
+    </row>
+    <row r="515">
+      <c r="A515" s="3" t="inlineStr"/>
+      <c r="B515" s="3" t="inlineStr">
+        <is>
+          <t>Saboneria</t>
+        </is>
+      </c>
+      <c r="C515" s="3" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D515" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcia M. Martí Escursell</t>
+        </is>
+      </c>
+      <c r="E515" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="F515" s="3" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G515" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="H515" s="3" t="inlineStr">
+        <is>
+          <t>41.5395</t>
+        </is>
+      </c>
+      <c r="I515" s="3" t="inlineStr">
+        <is>
+          <t>2.1095</t>
+        </is>
+      </c>
+      <c r="J515" s="3" t="inlineStr"/>
+      <c r="K515" s="3" t="inlineStr"/>
+      <c r="L515" s="3" t="inlineStr"/>
+      <c r="M515" s="3" t="inlineStr">
+        <is>
+          <t>farmacias_2026</t>
+        </is>
+      </c>
+      <c r="N515" s="3" t="inlineStr"/>
+      <c r="O515" s="3" t="inlineStr"/>
+      <c r="P515" s="3" t="inlineStr">
+        <is>
+          <t>Saboneria 127</t>
+        </is>
+      </c>
+      <c r="Q515" s="3" t="inlineStr"/>
+    </row>
+    <row r="516">
+      <c r="A516" s="2" t="inlineStr"/>
+      <c r="B516" s="2" t="inlineStr">
+        <is>
+          <t>Carretera de Prat de Lluçanès</t>
+        </is>
+      </c>
+      <c r="C516" s="2" t="inlineStr">
+        <is>
+          <t>84 local B</t>
+        </is>
+      </c>
+      <c r="D516" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcia CR Prat de Lluçanès 84</t>
+        </is>
+      </c>
+      <c r="E516" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="F516" s="2" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G516" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="H516" s="2" t="inlineStr">
+        <is>
+          <t>41.5605</t>
+        </is>
+      </c>
+      <c r="I516" s="2" t="inlineStr">
+        <is>
+          <t>2.1025</t>
+        </is>
+      </c>
+      <c r="J516" s="2" t="inlineStr"/>
+      <c r="K516" s="2" t="inlineStr"/>
+      <c r="L516" s="2" t="inlineStr"/>
+      <c r="M516" s="2" t="inlineStr">
+        <is>
+          <t>farmacias_2026</t>
+        </is>
+      </c>
+      <c r="N516" s="2" t="inlineStr"/>
+      <c r="O516" s="2" t="inlineStr"/>
+      <c r="P516" s="2" t="inlineStr">
+        <is>
+          <t>Carretera de Prat de Lluçanès 84 local B</t>
+        </is>
+      </c>
+      <c r="Q516" s="2" t="inlineStr"/>
+    </row>
+    <row r="517">
+      <c r="A517" s="3" t="inlineStr"/>
+      <c r="B517" s="3" t="inlineStr">
+        <is>
+          <t>Carrer de Sant Isidor</t>
+        </is>
+      </c>
+      <c r="C517" s="3" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D517" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcia M. Mora Palà</t>
+        </is>
+      </c>
+      <c r="E517" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="F517" s="3" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G517" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="H517" s="3" t="inlineStr">
+        <is>
+          <t>41.553</t>
+        </is>
+      </c>
+      <c r="I517" s="3" t="inlineStr">
+        <is>
+          <t>2.0845</t>
+        </is>
+      </c>
+      <c r="J517" s="3" t="inlineStr"/>
+      <c r="K517" s="3" t="inlineStr"/>
+      <c r="L517" s="3" t="inlineStr"/>
+      <c r="M517" s="3" t="inlineStr">
+        <is>
+          <t>farmacias_2026</t>
+        </is>
+      </c>
+      <c r="N517" s="3" t="inlineStr"/>
+      <c r="O517" s="3" t="inlineStr"/>
+      <c r="P517" s="3" t="inlineStr">
+        <is>
+          <t>Carrer de Sant Isidor 80</t>
+        </is>
+      </c>
+      <c r="Q517" s="3" t="inlineStr"/>
+    </row>
+    <row r="518">
+      <c r="A518" s="2" t="inlineStr"/>
+      <c r="B518" s="2" t="inlineStr">
+        <is>
+          <t>Campoamor</t>
+        </is>
+      </c>
+      <c r="C518" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D518" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcia R. Bernaldo Bech</t>
+        </is>
+      </c>
+      <c r="E518" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="F518" s="2" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G518" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="H518" s="2" t="inlineStr">
+        <is>
+          <t>41.5395</t>
+        </is>
+      </c>
+      <c r="I518" s="2" t="inlineStr">
+        <is>
+          <t>2.1095</t>
+        </is>
+      </c>
+      <c r="J518" s="2" t="inlineStr"/>
+      <c r="K518" s="2" t="inlineStr"/>
+      <c r="L518" s="2" t="inlineStr"/>
+      <c r="M518" s="2" t="inlineStr">
+        <is>
+          <t>farmacias_2026</t>
+        </is>
+      </c>
+      <c r="N518" s="2" t="inlineStr"/>
+      <c r="O518" s="2" t="inlineStr"/>
+      <c r="P518" s="2" t="inlineStr">
+        <is>
+          <t>Campoamor 40</t>
+        </is>
+      </c>
+      <c r="Q518" s="2" t="inlineStr"/>
+    </row>
+    <row r="519">
+      <c r="A519" s="3" t="inlineStr"/>
+      <c r="B519" s="3" t="inlineStr">
+        <is>
+          <t>Ronda Sta. Maria</t>
+        </is>
+      </c>
+      <c r="C519" s="3" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D519" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcia Esteban-Lopera</t>
+        </is>
+      </c>
+      <c r="E519" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="F519" s="3" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G519" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="H519" s="3" t="inlineStr">
+        <is>
+          <t>41.5395</t>
+        </is>
+      </c>
+      <c r="I519" s="3" t="inlineStr">
+        <is>
+          <t>2.1095</t>
+        </is>
+      </c>
+      <c r="J519" s="3" t="inlineStr"/>
+      <c r="K519" s="3" t="inlineStr"/>
+      <c r="L519" s="3" t="inlineStr"/>
+      <c r="M519" s="3" t="inlineStr">
+        <is>
+          <t>farmacias_2026</t>
+        </is>
+      </c>
+      <c r="N519" s="3" t="inlineStr"/>
+      <c r="O519" s="3" t="inlineStr"/>
+      <c r="P519" s="3" t="inlineStr">
+        <is>
+          <t>Ronda Sta. Maria 28</t>
+        </is>
+      </c>
+      <c r="Q519" s="3" t="inlineStr"/>
+    </row>
+    <row r="520">
+      <c r="A520" s="2" t="inlineStr"/>
+      <c r="B520" s="2" t="inlineStr">
+        <is>
+          <t>Tenerife</t>
+        </is>
+      </c>
+      <c r="C520" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D520" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcia Tenerife 52</t>
+        </is>
+      </c>
+      <c r="E520" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="F520" s="2" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G520" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="H520" s="2" t="inlineStr">
+        <is>
+          <t>41.553</t>
+        </is>
+      </c>
+      <c r="I520" s="2" t="inlineStr">
+        <is>
+          <t>2.0875</t>
+        </is>
+      </c>
+      <c r="J520" s="2" t="inlineStr"/>
+      <c r="K520" s="2" t="inlineStr"/>
+      <c r="L520" s="2" t="inlineStr"/>
+      <c r="M520" s="2" t="inlineStr">
+        <is>
+          <t>farmacias_2026</t>
+        </is>
+      </c>
+      <c r="N520" s="2" t="inlineStr"/>
+      <c r="O520" s="2" t="inlineStr"/>
+      <c r="P520" s="2" t="inlineStr">
+        <is>
+          <t>Tenerife 52</t>
+        </is>
+      </c>
+      <c r="Q520" s="2" t="inlineStr"/>
+    </row>
+    <row r="521">
+      <c r="A521" s="3" t="inlineStr"/>
+      <c r="B521" s="3" t="inlineStr">
+        <is>
+          <t>Carrer de Balmes</t>
+        </is>
+      </c>
+      <c r="C521" s="3" t="inlineStr">
+        <is>
+          <t>83-85</t>
+        </is>
+      </c>
+      <c r="D521" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcia Roca-Sala</t>
+        </is>
+      </c>
+      <c r="E521" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="F521" s="3" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G521" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="H521" s="3" t="inlineStr">
+        <is>
+          <t>41.538</t>
+        </is>
+      </c>
+      <c r="I521" s="3" t="inlineStr">
+        <is>
+          <t>2.114</t>
+        </is>
+      </c>
+      <c r="J521" s="3" t="inlineStr"/>
+      <c r="K521" s="3" t="inlineStr"/>
+      <c r="L521" s="3" t="inlineStr"/>
+      <c r="M521" s="3" t="inlineStr">
+        <is>
+          <t>farmacias_2026</t>
+        </is>
+      </c>
+      <c r="N521" s="3" t="inlineStr"/>
+      <c r="O521" s="3" t="inlineStr"/>
+      <c r="P521" s="3" t="inlineStr">
+        <is>
+          <t>Carrer de Balmes 83-85</t>
+        </is>
+      </c>
+      <c r="Q521" s="3" t="inlineStr"/>
+    </row>
+    <row r="522">
+      <c r="A522" s="2" t="inlineStr"/>
+      <c r="B522" s="2" t="inlineStr">
+        <is>
+          <t>Rambla Sabadell</t>
+        </is>
+      </c>
+      <c r="C522" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D522" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcia Mercedes Segalás Carreras</t>
+        </is>
+      </c>
+      <c r="E522" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="F522" s="2" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G522" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="H522" s="2" t="inlineStr">
+        <is>
+          <t>41.5485</t>
+        </is>
+      </c>
+      <c r="I522" s="2" t="inlineStr">
+        <is>
+          <t>2.109</t>
+        </is>
+      </c>
+      <c r="J522" s="2" t="inlineStr"/>
+      <c r="K522" s="2" t="inlineStr"/>
+      <c r="L522" s="2" t="inlineStr"/>
+      <c r="M522" s="2" t="inlineStr">
+        <is>
+          <t>farmacias_2026</t>
+        </is>
+      </c>
+      <c r="N522" s="2" t="inlineStr"/>
+      <c r="O522" s="2" t="inlineStr"/>
+      <c r="P522" s="2" t="inlineStr">
+        <is>
+          <t>Rambla Sabadell 26</t>
+        </is>
+      </c>
+      <c r="Q522" s="2" t="inlineStr"/>
+    </row>
+    <row r="523">
+      <c r="A523" s="3" t="inlineStr"/>
+      <c r="B523" s="3" t="inlineStr">
+        <is>
+          <t>Ronda Ponent</t>
+        </is>
+      </c>
+      <c r="C523" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D523" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcia Corominas</t>
+        </is>
+      </c>
+      <c r="E523" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="F523" s="3" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G523" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="H523" s="3" t="inlineStr">
+        <is>
+          <t>41.553</t>
+        </is>
+      </c>
+      <c r="I523" s="3" t="inlineStr">
+        <is>
+          <t>2.0845</t>
+        </is>
+      </c>
+      <c r="J523" s="3" t="inlineStr"/>
+      <c r="K523" s="3" t="inlineStr"/>
+      <c r="L523" s="3" t="inlineStr"/>
+      <c r="M523" s="3" t="inlineStr">
+        <is>
+          <t>farmacias_2026</t>
+        </is>
+      </c>
+      <c r="N523" s="3" t="inlineStr"/>
+      <c r="O523" s="3" t="inlineStr"/>
+      <c r="P523" s="3" t="inlineStr">
+        <is>
+          <t>Ronda Ponent 1</t>
+        </is>
+      </c>
+      <c r="Q523" s="3" t="inlineStr"/>
+    </row>
+    <row r="524">
+      <c r="A524" s="2" t="inlineStr"/>
+      <c r="B524" s="2" t="inlineStr">
+        <is>
+          <t>Florit</t>
+        </is>
+      </c>
+      <c r="C524" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D524" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcia J. Tous Geulen</t>
+        </is>
+      </c>
+      <c r="E524" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="F524" s="2" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G524" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="H524" s="2" t="inlineStr">
+        <is>
+          <t>41.5605</t>
+        </is>
+      </c>
+      <c r="I524" s="2" t="inlineStr">
+        <is>
+          <t>2.1025</t>
+        </is>
+      </c>
+      <c r="J524" s="2" t="inlineStr"/>
+      <c r="K524" s="2" t="inlineStr"/>
+      <c r="L524" s="2" t="inlineStr"/>
+      <c r="M524" s="2" t="inlineStr">
+        <is>
+          <t>farmacias_2026</t>
+        </is>
+      </c>
+      <c r="N524" s="2" t="inlineStr"/>
+      <c r="O524" s="2" t="inlineStr"/>
+      <c r="P524" s="2" t="inlineStr">
+        <is>
+          <t>Florit 29</t>
+        </is>
+      </c>
+      <c r="Q524" s="2" t="inlineStr"/>
+    </row>
+    <row r="525">
+      <c r="A525" s="3" t="inlineStr"/>
+      <c r="B525" s="3" t="inlineStr">
+        <is>
+          <t>Carretera de Barcelona</t>
+        </is>
+      </c>
+      <c r="C525" s="3" t="inlineStr">
+        <is>
+          <t>560</t>
+        </is>
+      </c>
+      <c r="D525" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcia M. Brustenga Fortuny</t>
+        </is>
+      </c>
+      <c r="E525" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="F525" s="3" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G525" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="H525" s="3" t="inlineStr">
+        <is>
+          <t>41.5395</t>
+        </is>
+      </c>
+      <c r="I525" s="3" t="inlineStr">
+        <is>
+          <t>2.1095</t>
+        </is>
+      </c>
+      <c r="J525" s="3" t="inlineStr"/>
+      <c r="K525" s="3" t="inlineStr"/>
+      <c r="L525" s="3" t="inlineStr"/>
+      <c r="M525" s="3" t="inlineStr">
+        <is>
+          <t>farmacias_2026</t>
+        </is>
+      </c>
+      <c r="N525" s="3" t="inlineStr"/>
+      <c r="O525" s="3" t="inlineStr"/>
+      <c r="P525" s="3" t="inlineStr">
+        <is>
+          <t>Carretera de Barcelona 560</t>
+        </is>
+      </c>
+      <c r="Q525" s="3" t="inlineStr"/>
+    </row>
+    <row r="526">
+      <c r="A526" s="2" t="inlineStr"/>
+      <c r="B526" s="2" t="inlineStr">
+        <is>
+          <t>Avinguda de Matadepera</t>
+        </is>
+      </c>
+      <c r="C526" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D526" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcia E. Baqués Roviralta</t>
+        </is>
+      </c>
+      <c r="E526" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="F526" s="2" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G526" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="H526" s="2" t="inlineStr">
+        <is>
+          <t>41.564</t>
+        </is>
+      </c>
+      <c r="I526" s="2" t="inlineStr">
+        <is>
+          <t>2.0905</t>
+        </is>
+      </c>
+      <c r="J526" s="2" t="inlineStr"/>
+      <c r="K526" s="2" t="inlineStr"/>
+      <c r="L526" s="2" t="inlineStr"/>
+      <c r="M526" s="2" t="inlineStr">
+        <is>
+          <t>farmacias_2026</t>
+        </is>
+      </c>
+      <c r="N526" s="2" t="inlineStr"/>
+      <c r="O526" s="2" t="inlineStr"/>
+      <c r="P526" s="2" t="inlineStr">
+        <is>
+          <t>Avinguda de Matadepera 7</t>
+        </is>
+      </c>
+      <c r="Q526" s="2" t="inlineStr"/>
+    </row>
+    <row r="527">
+      <c r="A527" s="3" t="inlineStr"/>
+      <c r="B527" s="3" t="inlineStr">
+        <is>
+          <t>Goya</t>
+        </is>
+      </c>
+      <c r="C527" s="3" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D527" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcia E. González Carnicer</t>
+        </is>
+      </c>
+      <c r="E527" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="F527" s="3" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G527" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="H527" s="3" t="inlineStr">
+        <is>
+          <t>41.5395</t>
+        </is>
+      </c>
+      <c r="I527" s="3" t="inlineStr">
+        <is>
+          <t>2.1095</t>
+        </is>
+      </c>
+      <c r="J527" s="3" t="inlineStr"/>
+      <c r="K527" s="3" t="inlineStr"/>
+      <c r="L527" s="3" t="inlineStr"/>
+      <c r="M527" s="3" t="inlineStr">
+        <is>
+          <t>farmacias_2026</t>
+        </is>
+      </c>
+      <c r="N527" s="3" t="inlineStr"/>
+      <c r="O527" s="3" t="inlineStr"/>
+      <c r="P527" s="3" t="inlineStr">
+        <is>
+          <t>Goya 62</t>
+        </is>
+      </c>
+      <c r="Q527" s="3" t="inlineStr"/>
+    </row>
+    <row r="528">
+      <c r="A528" s="2" t="inlineStr"/>
+      <c r="B528" s="2" t="inlineStr">
+        <is>
+          <t>Santiago Segura</t>
+        </is>
+      </c>
+      <c r="C528" s="2" t="inlineStr">
+        <is>
+          <t>8-10</t>
+        </is>
+      </c>
+      <c r="D528" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcia A. García Sala</t>
+        </is>
+      </c>
+      <c r="E528" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="F528" s="2" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G528" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="H528" s="2" t="inlineStr">
+        <is>
+          <t>41.564</t>
+        </is>
+      </c>
+      <c r="I528" s="2" t="inlineStr">
+        <is>
+          <t>2.0905</t>
+        </is>
+      </c>
+      <c r="J528" s="2" t="inlineStr"/>
+      <c r="K528" s="2" t="inlineStr"/>
+      <c r="L528" s="2" t="inlineStr"/>
+      <c r="M528" s="2" t="inlineStr">
+        <is>
+          <t>farmacias_2026</t>
+        </is>
+      </c>
+      <c r="N528" s="2" t="inlineStr"/>
+      <c r="O528" s="2" t="inlineStr"/>
+      <c r="P528" s="2" t="inlineStr">
+        <is>
+          <t>Santiago Segura 8-10</t>
+        </is>
+      </c>
+      <c r="Q528" s="2" t="inlineStr"/>
+    </row>
+    <row r="529">
+      <c r="A529" s="3" t="inlineStr"/>
+      <c r="B529" s="3" t="inlineStr">
+        <is>
+          <t>Sant Vicenç de Paul</t>
+        </is>
+      </c>
+      <c r="C529" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D529" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcia L. Mercader Sanjuán</t>
+        </is>
+      </c>
+      <c r="E529" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="F529" s="3" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G529" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="H529" s="3" t="inlineStr">
+        <is>
+          <t>41.5395</t>
+        </is>
+      </c>
+      <c r="I529" s="3" t="inlineStr">
+        <is>
+          <t>2.1095</t>
+        </is>
+      </c>
+      <c r="J529" s="3" t="inlineStr"/>
+      <c r="K529" s="3" t="inlineStr"/>
+      <c r="L529" s="3" t="inlineStr"/>
+      <c r="M529" s="3" t="inlineStr">
+        <is>
+          <t>farmacias_2026</t>
+        </is>
+      </c>
+      <c r="N529" s="3" t="inlineStr"/>
+      <c r="O529" s="3" t="inlineStr"/>
+      <c r="P529" s="3" t="inlineStr">
+        <is>
+          <t>Sant Vicenç de Paul 1</t>
+        </is>
+      </c>
+      <c r="Q529" s="3" t="inlineStr"/>
+    </row>
+    <row r="530">
+      <c r="A530" s="2" t="inlineStr"/>
+      <c r="B530" s="2" t="inlineStr">
+        <is>
+          <t>Salústrio</t>
+        </is>
+      </c>
+      <c r="C530" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D530" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcia Marta Salvador Trilla</t>
+        </is>
+      </c>
+      <c r="E530" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="F530" s="2" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G530" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="H530" s="2" t="inlineStr">
+        <is>
+          <t>41.553</t>
+        </is>
+      </c>
+      <c r="I530" s="2" t="inlineStr">
+        <is>
+          <t>2.0845</t>
+        </is>
+      </c>
+      <c r="J530" s="2" t="inlineStr"/>
+      <c r="K530" s="2" t="inlineStr"/>
+      <c r="L530" s="2" t="inlineStr"/>
+      <c r="M530" s="2" t="inlineStr">
+        <is>
+          <t>farmacias_2026</t>
+        </is>
+      </c>
+      <c r="N530" s="2" t="inlineStr"/>
+      <c r="O530" s="2" t="inlineStr"/>
+      <c r="P530" s="2" t="inlineStr">
+        <is>
+          <t>Salústrio 2</t>
+        </is>
+      </c>
+      <c r="Q530" s="2" t="inlineStr"/>
+    </row>
+    <row r="531">
+      <c r="A531" s="3" t="inlineStr"/>
+      <c r="B531" s="3" t="inlineStr">
+        <is>
+          <t>Avinguda de Els Paraires</t>
+        </is>
+      </c>
+      <c r="C531" s="3" t="inlineStr">
+        <is>
+          <t>26 A</t>
+        </is>
+      </c>
+      <c r="D531" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcia Grimalt-Vives</t>
+        </is>
+      </c>
+      <c r="E531" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="F531" s="3" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G531" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="H531" s="3" t="inlineStr">
+        <is>
+          <t>41.553</t>
+        </is>
+      </c>
+      <c r="I531" s="3" t="inlineStr">
+        <is>
+          <t>2.0845</t>
+        </is>
+      </c>
+      <c r="J531" s="3" t="inlineStr"/>
+      <c r="K531" s="3" t="inlineStr"/>
+      <c r="L531" s="3" t="inlineStr"/>
+      <c r="M531" s="3" t="inlineStr">
+        <is>
+          <t>farmacias_2026</t>
+        </is>
+      </c>
+      <c r="N531" s="3" t="inlineStr"/>
+      <c r="O531" s="3" t="inlineStr"/>
+      <c r="P531" s="3" t="inlineStr">
+        <is>
+          <t>Avinguda de Els Paraires 26 A</t>
+        </is>
+      </c>
+      <c r="Q531" s="3" t="inlineStr"/>
+    </row>
+    <row r="532">
+      <c r="A532" s="2" t="inlineStr"/>
+      <c r="B532" s="2" t="inlineStr">
+        <is>
+          <t>Plaça de Espanya</t>
+        </is>
+      </c>
+      <c r="C532" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D532" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcia Argemí Alsina</t>
+        </is>
+      </c>
+      <c r="E532" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="F532" s="2" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G532" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="H532" s="2" t="inlineStr">
+        <is>
+          <t>41.564</t>
+        </is>
+      </c>
+      <c r="I532" s="2" t="inlineStr">
+        <is>
+          <t>2.0905</t>
+        </is>
+      </c>
+      <c r="J532" s="2" t="inlineStr"/>
+      <c r="K532" s="2" t="inlineStr"/>
+      <c r="L532" s="2" t="inlineStr"/>
+      <c r="M532" s="2" t="inlineStr">
+        <is>
+          <t>farmacias_2026</t>
+        </is>
+      </c>
+      <c r="N532" s="2" t="inlineStr"/>
+      <c r="O532" s="2" t="inlineStr"/>
+      <c r="P532" s="2" t="inlineStr">
+        <is>
+          <t>Plaça de Espanya 2</t>
+        </is>
+      </c>
+      <c r="Q532" s="2" t="inlineStr"/>
+    </row>
+    <row r="533">
+      <c r="A533" s="3" t="inlineStr"/>
+      <c r="B533" s="3" t="inlineStr">
+        <is>
+          <t>Candanchú</t>
+        </is>
+      </c>
+      <c r="C533" s="3" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D533" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcia J. de Càceres Botello</t>
+        </is>
+      </c>
+      <c r="E533" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="F533" s="3" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G533" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="H533" s="3" t="inlineStr">
+        <is>
+          <t>41.564</t>
+        </is>
+      </c>
+      <c r="I533" s="3" t="inlineStr">
+        <is>
+          <t>2.0905</t>
+        </is>
+      </c>
+      <c r="J533" s="3" t="inlineStr"/>
+      <c r="K533" s="3" t="inlineStr"/>
+      <c r="L533" s="3" t="inlineStr"/>
+      <c r="M533" s="3" t="inlineStr">
+        <is>
+          <t>farmacias_2026</t>
+        </is>
+      </c>
+      <c r="N533" s="3" t="inlineStr"/>
+      <c r="O533" s="3" t="inlineStr"/>
+      <c r="P533" s="3" t="inlineStr">
+        <is>
+          <t>Candanchú 31</t>
+        </is>
+      </c>
+      <c r="Q533" s="3" t="inlineStr"/>
+    </row>
+    <row r="534">
+      <c r="A534" s="2" t="inlineStr"/>
+      <c r="B534" s="2" t="inlineStr">
+        <is>
+          <t>Carrer de València (Farmàcia)</t>
+        </is>
+      </c>
+      <c r="C534" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D534" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcia D. Girbau Muro</t>
+        </is>
+      </c>
+      <c r="E534" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="F534" s="2" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G534" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcies</t>
+        </is>
+      </c>
+      <c r="H534" s="2" t="inlineStr">
+        <is>
+          <t>41.564</t>
+        </is>
+      </c>
+      <c r="I534" s="2" t="inlineStr">
+        <is>
+          <t>2.0905</t>
+        </is>
+      </c>
+      <c r="J534" s="2" t="inlineStr"/>
+      <c r="K534" s="2" t="inlineStr"/>
+      <c r="L534" s="2" t="inlineStr"/>
+      <c r="M534" s="2" t="inlineStr">
+        <is>
+          <t>farmacias_2026</t>
+        </is>
+      </c>
+      <c r="N534" s="2" t="inlineStr"/>
+      <c r="O534" s="2" t="inlineStr"/>
+      <c r="P534" s="2" t="inlineStr">
+        <is>
+          <t>Carrer de València (Farmàcia) 19</t>
+        </is>
+      </c>
+      <c r="Q534" s="2" t="inlineStr"/>
+    </row>
+    <row r="535">
+      <c r="A535" s="3" t="inlineStr"/>
+      <c r="B535" s="3" t="inlineStr">
+        <is>
+          <t>Carrer de Sol i Padrís</t>
+        </is>
+      </c>
+      <c r="C535" s="3" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D535" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcia Ortopèdia A. Capdevila Bassols</t>
+        </is>
+      </c>
+      <c r="E535" s="3" t="inlineStr">
+        <is>
+          <t>Salut - Ortopèdia</t>
+        </is>
+      </c>
+      <c r="F535" s="3" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G535" s="3" t="inlineStr">
+        <is>
+          <t>Salut - Ortopèdia</t>
+        </is>
+      </c>
+      <c r="H535" s="3" t="inlineStr">
+        <is>
+          <t>41.538</t>
+        </is>
+      </c>
+      <c r="I535" s="3" t="inlineStr">
+        <is>
+          <t>2.114</t>
+        </is>
+      </c>
+      <c r="J535" s="3" t="inlineStr"/>
+      <c r="K535" s="3" t="inlineStr">
+        <is>
+          <t>937109112</t>
+        </is>
+      </c>
+      <c r="L535" s="3" t="inlineStr"/>
+      <c r="M535" s="3" t="inlineStr">
+        <is>
+          <t>WebSearch_2026</t>
+        </is>
+      </c>
+      <c r="N535" s="3" t="inlineStr"/>
+      <c r="O535" s="3" t="inlineStr"/>
+      <c r="P535" s="3" t="inlineStr">
+        <is>
+          <t>Carrer de Sol i Padrís 114</t>
+        </is>
+      </c>
+      <c r="Q535" s="3" t="inlineStr"/>
+    </row>
+    <row r="536">
+      <c r="A536" s="2" t="inlineStr"/>
+      <c r="B536" s="2" t="inlineStr">
+        <is>
+          <t>Carrer de València</t>
+        </is>
+      </c>
+      <c r="C536" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D536" s="2" t="inlineStr">
+        <is>
+          <t>Farmàcia Ortopèdia D. Girbau Muro</t>
+        </is>
+      </c>
+      <c r="E536" s="2" t="inlineStr">
+        <is>
+          <t>Salut - Ortopèdia</t>
+        </is>
+      </c>
+      <c r="F536" s="2" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G536" s="2" t="inlineStr">
+        <is>
+          <t>Salut - Ortopèdia</t>
+        </is>
+      </c>
+      <c r="H536" s="2" t="inlineStr">
+        <is>
+          <t>41.564</t>
+        </is>
+      </c>
+      <c r="I536" s="2" t="inlineStr">
+        <is>
+          <t>2.0905</t>
+        </is>
+      </c>
+      <c r="J536" s="2" t="inlineStr"/>
+      <c r="K536" s="2" t="inlineStr">
+        <is>
+          <t>937166238</t>
+        </is>
+      </c>
+      <c r="L536" s="2" t="inlineStr"/>
+      <c r="M536" s="2" t="inlineStr">
+        <is>
+          <t>WebSearch_2026</t>
+        </is>
+      </c>
+      <c r="N536" s="2" t="inlineStr"/>
+      <c r="O536" s="2" t="inlineStr"/>
+      <c r="P536" s="2" t="inlineStr">
+        <is>
+          <t>Carrer de València 19</t>
+        </is>
+      </c>
+      <c r="Q536" s="2" t="inlineStr"/>
+    </row>
+    <row r="537">
+      <c r="A537" s="3" t="inlineStr"/>
+      <c r="B537" s="3" t="inlineStr">
+        <is>
+          <t>Rambla Sabadell</t>
+        </is>
+      </c>
+      <c r="C537" s="3" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D537" s="3" t="inlineStr">
+        <is>
+          <t>Farmàcia Ortopèdia Segalás</t>
+        </is>
+      </c>
+      <c r="E537" s="3" t="inlineStr">
+        <is>
+          <t>Salut - Ortopèdia</t>
+        </is>
+      </c>
+      <c r="F537" s="3" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G537" s="3" t="inlineStr">
+        <is>
+          <t>Salut - Ortopèdia</t>
+        </is>
+      </c>
+      <c r="H537" s="3" t="inlineStr">
+        <is>
+          <t>41.5485</t>
+        </is>
+      </c>
+      <c r="I537" s="3" t="inlineStr">
+        <is>
+          <t>2.109</t>
+        </is>
+      </c>
+      <c r="J537" s="3" t="inlineStr">
+        <is>
+          <t>ortogrup.com</t>
+        </is>
+      </c>
+      <c r="K537" s="3" t="inlineStr">
+        <is>
+          <t>937257319</t>
+        </is>
+      </c>
+      <c r="L537" s="3" t="inlineStr"/>
+      <c r="M537" s="3" t="inlineStr">
+        <is>
+          <t>WebSearch_2026</t>
+        </is>
+      </c>
+      <c r="N537" s="3" t="inlineStr"/>
+      <c r="O537" s="3" t="inlineStr"/>
+      <c r="P537" s="3" t="inlineStr">
+        <is>
+          <t>Rambla Sabadell 26</t>
+        </is>
+      </c>
+      <c r="Q537" s="3" t="inlineStr"/>
+    </row>
+    <row r="538">
+      <c r="A538" s="2" t="inlineStr"/>
+      <c r="B538" s="2" t="inlineStr">
+        <is>
+          <t>Carrer de Calassanç Duran</t>
+        </is>
+      </c>
+      <c r="C538" s="2" t="inlineStr">
+        <is>
+          <t>6-8</t>
+        </is>
+      </c>
+      <c r="D538" s="2" t="inlineStr">
+        <is>
+          <t>Ortoservei</t>
+        </is>
+      </c>
+      <c r="E538" s="2" t="inlineStr">
+        <is>
+          <t>Salut - Ortopèdia</t>
+        </is>
+      </c>
+      <c r="F538" s="2" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G538" s="2" t="inlineStr">
+        <is>
+          <t>Salut - Ortopèdia</t>
+        </is>
+      </c>
+      <c r="H538" s="2" t="inlineStr">
+        <is>
+          <t>41.538</t>
+        </is>
+      </c>
+      <c r="I538" s="2" t="inlineStr">
+        <is>
+          <t>2.114</t>
+        </is>
+      </c>
+      <c r="J538" s="2" t="inlineStr"/>
+      <c r="K538" s="2" t="inlineStr">
+        <is>
+          <t>931936961</t>
+        </is>
+      </c>
+      <c r="L538" s="2" t="inlineStr"/>
+      <c r="M538" s="2" t="inlineStr">
+        <is>
+          <t>WebSearch_2026</t>
+        </is>
+      </c>
+      <c r="N538" s="2" t="inlineStr"/>
+      <c r="O538" s="2" t="inlineStr"/>
+      <c r="P538" s="2" t="inlineStr">
+        <is>
+          <t>Carrer de Calassanç Duran 6-8</t>
+        </is>
+      </c>
+      <c r="Q538" s="2" t="inlineStr"/>
+    </row>
+    <row r="539">
+      <c r="A539" s="3" t="inlineStr"/>
+      <c r="B539" s="3" t="inlineStr">
+        <is>
+          <t>Avinguda de Onze de Setembre</t>
+        </is>
+      </c>
+      <c r="C539" s="3" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="D539" s="3" t="inlineStr">
+        <is>
+          <t>SUMED Ortopèdia</t>
+        </is>
+      </c>
+      <c r="E539" s="3" t="inlineStr">
+        <is>
+          <t>Salut - Ortopèdia</t>
+        </is>
+      </c>
+      <c r="F539" s="3" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G539" s="3" t="inlineStr">
+        <is>
+          <t>Salut - Ortopèdia</t>
+        </is>
+      </c>
+      <c r="H539" s="3" t="inlineStr">
+        <is>
+          <t>41.5605</t>
+        </is>
+      </c>
+      <c r="I539" s="3" t="inlineStr">
+        <is>
+          <t>2.1025</t>
+        </is>
+      </c>
+      <c r="J539" s="3" t="inlineStr"/>
+      <c r="K539" s="3" t="inlineStr"/>
+      <c r="L539" s="3" t="inlineStr"/>
+      <c r="M539" s="3" t="inlineStr">
+        <is>
+          <t>WebSearch_2026</t>
+        </is>
+      </c>
+      <c r="N539" s="3" t="inlineStr"/>
+      <c r="O539" s="3" t="inlineStr"/>
+      <c r="P539" s="3" t="inlineStr">
+        <is>
+          <t>Avinguda de Onze de Setembre 143</t>
+        </is>
+      </c>
+      <c r="Q539" s="3" t="inlineStr"/>
+    </row>
+    <row r="540">
+      <c r="A540" s="2" t="inlineStr"/>
+      <c r="B540" s="2" t="inlineStr">
+        <is>
+          <t>Carrer de dels Valls</t>
+        </is>
+      </c>
+      <c r="C540" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D540" s="2" t="inlineStr">
+        <is>
+          <t>Ortopèdia Arrahona</t>
+        </is>
+      </c>
+      <c r="E540" s="2" t="inlineStr">
+        <is>
+          <t>Salut - Ortopèdia</t>
+        </is>
+      </c>
+      <c r="F540" s="2" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G540" s="2" t="inlineStr">
+        <is>
+          <t>Salut - Ortopèdia</t>
+        </is>
+      </c>
+      <c r="H540" s="2" t="inlineStr">
+        <is>
+          <t>41.5395</t>
+        </is>
+      </c>
+      <c r="I540" s="2" t="inlineStr">
+        <is>
+          <t>2.1095</t>
+        </is>
+      </c>
+      <c r="J540" s="2" t="inlineStr"/>
+      <c r="K540" s="2" t="inlineStr"/>
+      <c r="L540" s="2" t="inlineStr"/>
+      <c r="M540" s="2" t="inlineStr">
+        <is>
+          <t>WebSearch_2026</t>
+        </is>
+      </c>
+      <c r="N540" s="2" t="inlineStr"/>
+      <c r="O540" s="2" t="inlineStr"/>
+      <c r="P540" s="2" t="inlineStr">
+        <is>
+          <t>Carrer de dels Valls 2</t>
+        </is>
+      </c>
+      <c r="Q540" s="2" t="inlineStr"/>
+    </row>
+    <row r="541">
+      <c r="A541" s="3" t="inlineStr"/>
+      <c r="B541" s="3" t="inlineStr">
+        <is>
+          <t>Carretera de Prats de Lluçanès</t>
+        </is>
+      </c>
+      <c r="C541" s="3" t="inlineStr">
+        <is>
+          <t>143 loc.2</t>
+        </is>
+      </c>
+      <c r="D541" s="3" t="inlineStr">
+        <is>
+          <t>TI-SANA herboristeria</t>
+        </is>
+      </c>
+      <c r="E541" s="3" t="inlineStr">
+        <is>
+          <t>Herboristeries</t>
+        </is>
+      </c>
+      <c r="F541" s="3" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G541" s="3" t="inlineStr">
+        <is>
+          <t>Herboristeries</t>
+        </is>
+      </c>
+      <c r="H541" s="3" t="inlineStr">
+        <is>
+          <t>41.5605</t>
+        </is>
+      </c>
+      <c r="I541" s="3" t="inlineStr">
+        <is>
+          <t>2.1025</t>
+        </is>
+      </c>
+      <c r="J541" s="3" t="inlineStr"/>
+      <c r="K541" s="3" t="inlineStr"/>
+      <c r="L541" s="3" t="inlineStr"/>
+      <c r="M541" s="3" t="inlineStr">
+        <is>
+          <t>qdq_2026</t>
+        </is>
+      </c>
+      <c r="N541" s="3" t="inlineStr"/>
+      <c r="O541" s="3" t="inlineStr"/>
+      <c r="P541" s="3" t="inlineStr">
+        <is>
+          <t>Carretera de Prats de Lluçanès 143 loc.2</t>
+        </is>
+      </c>
+      <c r="Q541" s="3" t="inlineStr"/>
+    </row>
+    <row r="542">
+      <c r="A542" s="2" t="inlineStr"/>
+      <c r="B542" s="2" t="inlineStr">
+        <is>
+          <t>Carrer de Major</t>
+        </is>
+      </c>
+      <c r="C542" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D542" s="2" t="inlineStr">
+        <is>
+          <t>Dietètica Creu Alta</t>
+        </is>
+      </c>
+      <c r="E542" s="2" t="inlineStr">
+        <is>
+          <t>Herboristeries</t>
+        </is>
+      </c>
+      <c r="F542" s="2" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G542" s="2" t="inlineStr">
+        <is>
+          <t>Herboristeries</t>
+        </is>
+      </c>
+      <c r="H542" s="2" t="inlineStr">
+        <is>
+          <t>41.5605</t>
+        </is>
+      </c>
+      <c r="I542" s="2" t="inlineStr">
+        <is>
+          <t>2.1025</t>
+        </is>
+      </c>
+      <c r="J542" s="2" t="inlineStr"/>
+      <c r="K542" s="2" t="inlineStr"/>
+      <c r="L542" s="2" t="inlineStr"/>
+      <c r="M542" s="2" t="inlineStr">
+        <is>
+          <t>qdq_2026</t>
+        </is>
+      </c>
+      <c r="N542" s="2" t="inlineStr"/>
+      <c r="O542" s="2" t="inlineStr"/>
+      <c r="P542" s="2" t="inlineStr">
+        <is>
+          <t>Carrer de Major 23</t>
+        </is>
+      </c>
+      <c r="Q542" s="2" t="inlineStr"/>
+    </row>
+    <row r="543">
+      <c r="A543" s="3" t="inlineStr"/>
+      <c r="B543" s="3" t="inlineStr">
+        <is>
+          <t>Carrer de Sant Isidor</t>
+        </is>
+      </c>
+      <c r="C543" s="3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D543" s="3" t="inlineStr">
+        <is>
+          <t>Can Rull herboristeria</t>
+        </is>
+      </c>
+      <c r="E543" s="3" t="inlineStr">
+        <is>
+          <t>Herboristeries</t>
+        </is>
+      </c>
+      <c r="F543" s="3" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G543" s="3" t="inlineStr">
+        <is>
+          <t>Herboristeries</t>
+        </is>
+      </c>
+      <c r="H543" s="3" t="inlineStr">
+        <is>
+          <t>41.553</t>
+        </is>
+      </c>
+      <c r="I543" s="3" t="inlineStr">
+        <is>
+          <t>2.0845</t>
+        </is>
+      </c>
+      <c r="J543" s="3" t="inlineStr"/>
+      <c r="K543" s="3" t="inlineStr"/>
+      <c r="L543" s="3" t="inlineStr"/>
+      <c r="M543" s="3" t="inlineStr">
+        <is>
+          <t>qdq_2026</t>
+        </is>
+      </c>
+      <c r="N543" s="3" t="inlineStr"/>
+      <c r="O543" s="3" t="inlineStr"/>
+      <c r="P543" s="3" t="inlineStr">
+        <is>
+          <t>Carrer de Sant Isidor 25</t>
+        </is>
+      </c>
+      <c r="Q543" s="3" t="inlineStr"/>
+    </row>
+    <row r="544">
+      <c r="A544" s="2" t="inlineStr"/>
+      <c r="B544" s="2" t="inlineStr">
+        <is>
+          <t>Carrer de La Palma</t>
+        </is>
+      </c>
+      <c r="C544" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D544" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Jade Herboristeria</t>
+        </is>
+      </c>
+      <c r="E544" s="2" t="inlineStr">
+        <is>
+          <t>Herboristeries</t>
+        </is>
+      </c>
+      <c r="F544" s="2" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G544" s="2" t="inlineStr">
+        <is>
+          <t>Herboristeries</t>
+        </is>
+      </c>
+      <c r="H544" s="2" t="inlineStr">
+        <is>
+          <t>41.553</t>
+        </is>
+      </c>
+      <c r="I544" s="2" t="inlineStr">
+        <is>
+          <t>2.0875</t>
+        </is>
+      </c>
+      <c r="J544" s="2" t="inlineStr"/>
+      <c r="K544" s="2" t="inlineStr"/>
+      <c r="L544" s="2" t="inlineStr"/>
+      <c r="M544" s="2" t="inlineStr">
+        <is>
+          <t>qdq_2026</t>
+        </is>
+      </c>
+      <c r="N544" s="2" t="inlineStr"/>
+      <c r="O544" s="2" t="inlineStr"/>
+      <c r="P544" s="2" t="inlineStr">
+        <is>
+          <t>Carrer de La Palma 43</t>
+        </is>
+      </c>
+      <c r="Q544" s="2" t="inlineStr"/>
+    </row>
+    <row r="545">
+      <c r="A545" s="3" t="inlineStr"/>
+      <c r="B545" s="3" t="inlineStr">
+        <is>
+          <t>Carrer de Rosa</t>
+        </is>
+      </c>
+      <c r="C545" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D545" s="3" t="inlineStr">
+        <is>
+          <t>Artigas Cortajussa herbolisteria</t>
+        </is>
+      </c>
+      <c r="E545" s="3" t="inlineStr">
+        <is>
+          <t>Herboristeries</t>
+        </is>
+      </c>
+      <c r="F545" s="3" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G545" s="3" t="inlineStr">
+        <is>
+          <t>Herboristeries</t>
+        </is>
+      </c>
+      <c r="H545" s="3" t="inlineStr">
+        <is>
+          <t>41.5485</t>
+        </is>
+      </c>
+      <c r="I545" s="3" t="inlineStr">
+        <is>
+          <t>2.109</t>
+        </is>
+      </c>
+      <c r="J545" s="3" t="inlineStr"/>
+      <c r="K545" s="3" t="inlineStr"/>
+      <c r="L545" s="3" t="inlineStr"/>
+      <c r="M545" s="3" t="inlineStr">
+        <is>
+          <t>qdq_2026</t>
+        </is>
+      </c>
+      <c r="N545" s="3" t="inlineStr"/>
+      <c r="O545" s="3" t="inlineStr"/>
+      <c r="P545" s="3" t="inlineStr">
+        <is>
+          <t>Carrer de Rosa 12</t>
+        </is>
+      </c>
+      <c r="Q545" s="3" t="inlineStr"/>
+    </row>
+    <row r="546">
+      <c r="A546" s="2" t="inlineStr"/>
+      <c r="B546" s="2" t="inlineStr">
+        <is>
+          <t>Carrer de Lluçanès</t>
+        </is>
+      </c>
+      <c r="C546" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D546" s="2" t="inlineStr">
+        <is>
+          <t>Dalia Herbodiètetics</t>
+        </is>
+      </c>
+      <c r="E546" s="2" t="inlineStr">
+        <is>
+          <t>Herboristeries</t>
+        </is>
+      </c>
+      <c r="F546" s="2" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G546" s="2" t="inlineStr">
+        <is>
+          <t>Herboristeries</t>
+        </is>
+      </c>
+      <c r="H546" s="2" t="inlineStr">
+        <is>
+          <t>41.564</t>
+        </is>
+      </c>
+      <c r="I546" s="2" t="inlineStr">
+        <is>
+          <t>2.0905</t>
+        </is>
+      </c>
+      <c r="J546" s="2" t="inlineStr"/>
+      <c r="K546" s="2" t="inlineStr"/>
+      <c r="L546" s="2" t="inlineStr"/>
+      <c r="M546" s="2" t="inlineStr">
+        <is>
+          <t>qdq_2026</t>
+        </is>
+      </c>
+      <c r="N546" s="2" t="inlineStr"/>
+      <c r="O546" s="2" t="inlineStr"/>
+      <c r="P546" s="2" t="inlineStr">
+        <is>
+          <t>Carrer de Lluçanès 23</t>
+        </is>
+      </c>
+      <c r="Q546" s="2" t="inlineStr"/>
+    </row>
+    <row r="547">
+      <c r="A547" s="3" t="inlineStr"/>
+      <c r="B547" s="3" t="inlineStr">
+        <is>
+          <t>Carrer de Gràcia</t>
+        </is>
+      </c>
+      <c r="C547" s="3" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D547" s="3" t="inlineStr">
+        <is>
+          <t>Sílvia López Pérez herboristeria</t>
+        </is>
+      </c>
+      <c r="E547" s="3" t="inlineStr">
+        <is>
+          <t>Herboristeries</t>
+        </is>
+      </c>
+      <c r="F547" s="3" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G547" s="3" t="inlineStr">
+        <is>
+          <t>Herboristeries</t>
+        </is>
+      </c>
+      <c r="H547" s="3" t="inlineStr">
+        <is>
+          <t>41.5485</t>
+        </is>
+      </c>
+      <c r="I547" s="3" t="inlineStr">
+        <is>
+          <t>2.109</t>
+        </is>
+      </c>
+      <c r="J547" s="3" t="inlineStr"/>
+      <c r="K547" s="3" t="inlineStr"/>
+      <c r="L547" s="3" t="inlineStr"/>
+      <c r="M547" s="3" t="inlineStr">
+        <is>
+          <t>qdq_2026</t>
+        </is>
+      </c>
+      <c r="N547" s="3" t="inlineStr"/>
+      <c r="O547" s="3" t="inlineStr"/>
+      <c r="P547" s="3" t="inlineStr">
+        <is>
+          <t>Carrer de Gràcia 66</t>
+        </is>
+      </c>
+      <c r="Q547" s="3" t="inlineStr"/>
+    </row>
+    <row r="548">
+      <c r="A548" s="2" t="inlineStr"/>
+      <c r="B548" s="2" t="inlineStr">
+        <is>
+          <t>Avinguda de Matadepera</t>
+        </is>
+      </c>
+      <c r="C548" s="2" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D548" s="2" t="inlineStr">
+        <is>
+          <t>Centre Dietètic Ca n'Oriac</t>
+        </is>
+      </c>
+      <c r="E548" s="2" t="inlineStr">
+        <is>
+          <t>Herboristeries</t>
+        </is>
+      </c>
+      <c r="F548" s="2" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G548" s="2" t="inlineStr">
+        <is>
+          <t>Herboristeries</t>
+        </is>
+      </c>
+      <c r="H548" s="2" t="inlineStr">
+        <is>
+          <t>41.564</t>
+        </is>
+      </c>
+      <c r="I548" s="2" t="inlineStr">
+        <is>
+          <t>2.0905</t>
+        </is>
+      </c>
+      <c r="J548" s="2" t="inlineStr"/>
+      <c r="K548" s="2" t="inlineStr"/>
+      <c r="L548" s="2" t="inlineStr"/>
+      <c r="M548" s="2" t="inlineStr">
+        <is>
+          <t>qdq_2026</t>
+        </is>
+      </c>
+      <c r="N548" s="2" t="inlineStr"/>
+      <c r="O548" s="2" t="inlineStr"/>
+      <c r="P548" s="2" t="inlineStr">
+        <is>
+          <t>Avinguda de Matadepera 153</t>
+        </is>
+      </c>
+      <c r="Q548" s="2" t="inlineStr"/>
+    </row>
+    <row r="549">
+      <c r="A549" s="3" t="inlineStr"/>
+      <c r="B549" s="3" t="inlineStr">
+        <is>
+          <t>Carrer de Sarajevo</t>
+        </is>
+      </c>
+      <c r="C549" s="3" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="D549" s="3" t="inlineStr">
+        <is>
+          <t>La Vecina Canaria herboristeria</t>
+        </is>
+      </c>
+      <c r="E549" s="3" t="inlineStr">
+        <is>
+          <t>Herboristeries</t>
+        </is>
+      </c>
+      <c r="F549" s="3" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G549" s="3" t="inlineStr">
+        <is>
+          <t>Herboristeries</t>
+        </is>
+      </c>
+      <c r="H549" s="3" t="inlineStr">
+        <is>
+          <t>41.553</t>
+        </is>
+      </c>
+      <c r="I549" s="3" t="inlineStr">
+        <is>
+          <t>2.0845</t>
+        </is>
+      </c>
+      <c r="J549" s="3" t="inlineStr"/>
+      <c r="K549" s="3" t="inlineStr"/>
+      <c r="L549" s="3" t="inlineStr"/>
+      <c r="M549" s="3" t="inlineStr">
+        <is>
+          <t>qdq_2026</t>
+        </is>
+      </c>
+      <c r="N549" s="3" t="inlineStr"/>
+      <c r="O549" s="3" t="inlineStr"/>
+      <c r="P549" s="3" t="inlineStr">
+        <is>
+          <t>Carrer de Sarajevo 151</t>
+        </is>
+      </c>
+      <c r="Q549" s="3" t="inlineStr"/>
+    </row>
+    <row r="550">
+      <c r="A550" s="2" t="inlineStr"/>
+      <c r="B550" s="2" t="inlineStr">
+        <is>
+          <t>Carrer de Sau</t>
+        </is>
+      </c>
+      <c r="C550" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D550" s="2" t="inlineStr">
+        <is>
+          <t>Herboristeria Consuelo</t>
+        </is>
+      </c>
+      <c r="E550" s="2" t="inlineStr">
+        <is>
+          <t>Herboristeries</t>
+        </is>
+      </c>
+      <c r="F550" s="2" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G550" s="2" t="inlineStr">
+        <is>
+          <t>Herboristeries</t>
+        </is>
+      </c>
+      <c r="H550" s="2" t="inlineStr">
+        <is>
+          <t>41.5475</t>
+        </is>
+      </c>
+      <c r="I550" s="2" t="inlineStr">
+        <is>
+          <t>2.107</t>
+        </is>
+      </c>
+      <c r="J550" s="2" t="inlineStr"/>
+      <c r="K550" s="2" t="inlineStr"/>
+      <c r="L550" s="2" t="inlineStr"/>
+      <c r="M550" s="2" t="inlineStr">
+        <is>
+          <t>qdq_2026</t>
+        </is>
+      </c>
+      <c r="N550" s="2" t="inlineStr"/>
+      <c r="O550" s="2" t="inlineStr"/>
+      <c r="P550" s="2" t="inlineStr">
+        <is>
+          <t>Carrer de Sau 93</t>
+        </is>
+      </c>
+      <c r="Q550" s="2" t="inlineStr"/>
+    </row>
+    <row r="551">
+      <c r="A551" s="3" t="inlineStr"/>
+      <c r="B551" s="3" t="inlineStr">
+        <is>
+          <t>Carrer de Agnès Armengol</t>
+        </is>
+      </c>
+      <c r="C551" s="3" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D551" s="3" t="inlineStr">
+        <is>
+          <t>Naturaly S.L. herboristeria</t>
+        </is>
+      </c>
+      <c r="E551" s="3" t="inlineStr">
+        <is>
+          <t>Herboristeries</t>
+        </is>
+      </c>
+      <c r="F551" s="3" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G551" s="3" t="inlineStr">
+        <is>
+          <t>Herboristeries</t>
+        </is>
+      </c>
+      <c r="H551" s="3" t="inlineStr">
+        <is>
+          <t>41.5605</t>
+        </is>
+      </c>
+      <c r="I551" s="3" t="inlineStr">
+        <is>
+          <t>2.1025</t>
+        </is>
+      </c>
+      <c r="J551" s="3" t="inlineStr"/>
+      <c r="K551" s="3" t="inlineStr"/>
+      <c r="L551" s="3" t="inlineStr"/>
+      <c r="M551" s="3" t="inlineStr">
+        <is>
+          <t>qdq_2026</t>
+        </is>
+      </c>
+      <c r="N551" s="3" t="inlineStr"/>
+      <c r="O551" s="3" t="inlineStr"/>
+      <c r="P551" s="3" t="inlineStr">
+        <is>
+          <t>Carrer de Agnès Armengol 26</t>
+        </is>
+      </c>
+      <c r="Q551" s="3" t="inlineStr"/>
+    </row>
+    <row r="552">
+      <c r="A552" s="2" t="inlineStr"/>
+      <c r="B552" s="2" t="inlineStr">
+        <is>
+          <t>Passeig de Fleming</t>
+        </is>
+      </c>
+      <c r="C552" s="2" t="inlineStr">
+        <is>
+          <t>8 bis</t>
+        </is>
+      </c>
+      <c r="D552" s="2" t="inlineStr">
+        <is>
+          <t>Naturcenter herboristeria</t>
+        </is>
+      </c>
+      <c r="E552" s="2" t="inlineStr">
+        <is>
+          <t>Herboristeries</t>
+        </is>
+      </c>
+      <c r="F552" s="2" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G552" s="2" t="inlineStr">
+        <is>
+          <t>Herboristeries</t>
+        </is>
+      </c>
+      <c r="H552" s="2" t="inlineStr">
+        <is>
+          <t>41.553</t>
+        </is>
+      </c>
+      <c r="I552" s="2" t="inlineStr">
+        <is>
+          <t>2.0845</t>
+        </is>
+      </c>
+      <c r="J552" s="2" t="inlineStr"/>
+      <c r="K552" s="2" t="inlineStr"/>
+      <c r="L552" s="2" t="inlineStr"/>
+      <c r="M552" s="2" t="inlineStr">
+        <is>
+          <t>qdq_2026</t>
+        </is>
+      </c>
+      <c r="N552" s="2" t="inlineStr"/>
+      <c r="O552" s="2" t="inlineStr"/>
+      <c r="P552" s="2" t="inlineStr">
+        <is>
+          <t>Passeig de Fleming 8 bis</t>
+        </is>
+      </c>
+      <c r="Q552" s="2" t="inlineStr"/>
+    </row>
+    <row r="553">
+      <c r="A553" s="3" t="inlineStr"/>
+      <c r="B553" s="3" t="inlineStr">
+        <is>
+          <t>Carrer de Sant Pau</t>
+        </is>
+      </c>
+      <c r="C553" s="3" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D553" s="3" t="inlineStr">
+        <is>
+          <t>Herboristeria Sant Pau</t>
+        </is>
+      </c>
+      <c r="E553" s="3" t="inlineStr">
+        <is>
+          <t>Herboristeries</t>
+        </is>
+      </c>
+      <c r="F553" s="3" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G553" s="3" t="inlineStr">
+        <is>
+          <t>Herboristeries</t>
+        </is>
+      </c>
+      <c r="H553" s="3" t="inlineStr">
+        <is>
+          <t>41.5485</t>
+        </is>
+      </c>
+      <c r="I553" s="3" t="inlineStr">
+        <is>
+          <t>2.109</t>
+        </is>
+      </c>
+      <c r="J553" s="3" t="inlineStr"/>
+      <c r="K553" s="3" t="inlineStr">
+        <is>
+          <t>937220826</t>
+        </is>
+      </c>
+      <c r="L553" s="3" t="inlineStr"/>
+      <c r="M553" s="3" t="inlineStr">
+        <is>
+          <t>qdq_2026</t>
+        </is>
+      </c>
+      <c r="N553" s="3" t="inlineStr"/>
+      <c r="O553" s="3" t="inlineStr"/>
+      <c r="P553" s="3" t="inlineStr">
+        <is>
+          <t>Carrer de Sant Pau 39</t>
+        </is>
+      </c>
+      <c r="Q553" s="3" t="inlineStr"/>
+    </row>
+    <row r="554">
+      <c r="A554" s="2" t="inlineStr"/>
+      <c r="B554" s="2" t="inlineStr">
+        <is>
+          <t>Carrer de Duran i Sors</t>
+        </is>
+      </c>
+      <c r="C554" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D554" s="2" t="inlineStr">
+        <is>
+          <t>Herboristeria Duran i Sors</t>
+        </is>
+      </c>
+      <c r="E554" s="2" t="inlineStr">
+        <is>
+          <t>Herboristeries</t>
+        </is>
+      </c>
+      <c r="F554" s="2" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G554" s="2" t="inlineStr">
+        <is>
+          <t>Herboristeries</t>
+        </is>
+      </c>
+      <c r="H554" s="2" t="inlineStr">
+        <is>
+          <t>41.5485</t>
+        </is>
+      </c>
+      <c r="I554" s="2" t="inlineStr">
+        <is>
+          <t>2.109</t>
+        </is>
+      </c>
+      <c r="J554" s="2" t="inlineStr"/>
+      <c r="K554" s="2" t="inlineStr">
+        <is>
+          <t>930310001</t>
+        </is>
+      </c>
+      <c r="L554" s="2" t="inlineStr"/>
+      <c r="M554" s="2" t="inlineStr">
+        <is>
+          <t>qdq_2026</t>
+        </is>
+      </c>
+      <c r="N554" s="2" t="inlineStr"/>
+      <c r="O554" s="2" t="inlineStr"/>
+      <c r="P554" s="2" t="inlineStr">
+        <is>
+          <t>Carrer de Duran i Sors 3</t>
+        </is>
+      </c>
+      <c r="Q554" s="2" t="inlineStr"/>
+    </row>
+    <row r="555">
+      <c r="A555" s="3" t="inlineStr"/>
+      <c r="B555" s="3" t="inlineStr">
+        <is>
+          <t>Carrer de Calderón</t>
+        </is>
+      </c>
+      <c r="C555" s="3" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D555" s="3" t="inlineStr">
+        <is>
+          <t>Herboristeria Calderón</t>
+        </is>
+      </c>
+      <c r="E555" s="3" t="inlineStr">
+        <is>
+          <t>Herboristeries</t>
+        </is>
+      </c>
+      <c r="F555" s="3" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G555" s="3" t="inlineStr">
+        <is>
+          <t>Herboristeries</t>
+        </is>
+      </c>
+      <c r="H555" s="3" t="inlineStr">
+        <is>
+          <t>41.5485</t>
+        </is>
+      </c>
+      <c r="I555" s="3" t="inlineStr">
+        <is>
+          <t>2.109</t>
+        </is>
+      </c>
+      <c r="J555" s="3" t="inlineStr"/>
+      <c r="K555" s="3" t="inlineStr">
+        <is>
+          <t>937276511</t>
+        </is>
+      </c>
+      <c r="L555" s="3" t="inlineStr"/>
+      <c r="M555" s="3" t="inlineStr">
+        <is>
+          <t>qdq_2026</t>
+        </is>
+      </c>
+      <c r="N555" s="3" t="inlineStr"/>
+      <c r="O555" s="3" t="inlineStr"/>
+      <c r="P555" s="3" t="inlineStr">
+        <is>
+          <t>Carrer de Calderón 52</t>
+        </is>
+      </c>
+      <c r="Q555" s="3" t="inlineStr"/>
+    </row>
+    <row r="556">
+      <c r="A556" s="2" t="inlineStr"/>
+      <c r="B556" s="2" t="inlineStr">
+        <is>
+          <t>Carrer de Sant Antoni</t>
+        </is>
+      </c>
+      <c r="C556" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D556" s="2" t="inlineStr">
+        <is>
+          <t>Herboristeria Sant Antoni</t>
+        </is>
+      </c>
+      <c r="E556" s="2" t="inlineStr">
+        <is>
+          <t>Herboristeries</t>
+        </is>
+      </c>
+      <c r="F556" s="2" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G556" s="2" t="inlineStr">
+        <is>
+          <t>Herboristeries</t>
+        </is>
+      </c>
+      <c r="H556" s="2" t="inlineStr">
+        <is>
+          <t>41.5485</t>
+        </is>
+      </c>
+      <c r="I556" s="2" t="inlineStr">
+        <is>
+          <t>2.109</t>
+        </is>
+      </c>
+      <c r="J556" s="2" t="inlineStr"/>
+      <c r="K556" s="2" t="inlineStr">
+        <is>
+          <t>937260710</t>
+        </is>
+      </c>
+      <c r="L556" s="2" t="inlineStr"/>
+      <c r="M556" s="2" t="inlineStr">
+        <is>
+          <t>qdq_2026</t>
+        </is>
+      </c>
+      <c r="N556" s="2" t="inlineStr"/>
+      <c r="O556" s="2" t="inlineStr"/>
+      <c r="P556" s="2" t="inlineStr">
+        <is>
+          <t>Carrer de Sant Antoni 11</t>
+        </is>
+      </c>
+      <c r="Q556" s="2" t="inlineStr"/>
+    </row>
+    <row r="557">
+      <c r="A557" s="3" t="inlineStr"/>
+      <c r="B557" s="3" t="inlineStr">
+        <is>
+          <t>Carretera de Barcelona</t>
+        </is>
+      </c>
+      <c r="C557" s="3" t="inlineStr">
+        <is>
+          <t>584</t>
+        </is>
+      </c>
+      <c r="D557" s="3" t="inlineStr">
+        <is>
+          <t>Herboristeria CR Barcelona 584</t>
+        </is>
+      </c>
+      <c r="E557" s="3" t="inlineStr">
+        <is>
+          <t>Herboristeries</t>
+        </is>
+      </c>
+      <c r="F557" s="3" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G557" s="3" t="inlineStr">
+        <is>
+          <t>Herboristeries</t>
+        </is>
+      </c>
+      <c r="H557" s="3" t="inlineStr">
+        <is>
+          <t>41.5395</t>
+        </is>
+      </c>
+      <c r="I557" s="3" t="inlineStr">
+        <is>
+          <t>2.1095</t>
+        </is>
+      </c>
+      <c r="J557" s="3" t="inlineStr"/>
+      <c r="K557" s="3" t="inlineStr">
+        <is>
+          <t>937123070</t>
+        </is>
+      </c>
+      <c r="L557" s="3" t="inlineStr"/>
+      <c r="M557" s="3" t="inlineStr">
+        <is>
+          <t>qdq_2026</t>
+        </is>
+      </c>
+      <c r="N557" s="3" t="inlineStr"/>
+      <c r="O557" s="3" t="inlineStr"/>
+      <c r="P557" s="3" t="inlineStr">
+        <is>
+          <t>Carretera de Barcelona 584</t>
+        </is>
+      </c>
+      <c r="Q557" s="3" t="inlineStr"/>
+    </row>
+    <row r="558">
+      <c r="A558" s="2" t="inlineStr"/>
+      <c r="B558" s="2" t="inlineStr">
+        <is>
+          <t>Avinguda de Barberà</t>
+        </is>
+      </c>
+      <c r="C558" s="2" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="D558" s="2" t="inlineStr">
+        <is>
+          <t>Herboristeria AV Barberà 309</t>
+        </is>
+      </c>
+      <c r="E558" s="2" t="inlineStr">
+        <is>
+          <t>Herboristeries</t>
+        </is>
+      </c>
+      <c r="F558" s="2" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G558" s="2" t="inlineStr">
+        <is>
+          <t>Herboristeries</t>
+        </is>
+      </c>
+      <c r="H558" s="2" t="inlineStr">
+        <is>
+          <t>41.5395</t>
+        </is>
+      </c>
+      <c r="I558" s="2" t="inlineStr">
+        <is>
+          <t>2.1095</t>
+        </is>
+      </c>
+      <c r="J558" s="2" t="inlineStr"/>
+      <c r="K558" s="2" t="inlineStr">
+        <is>
+          <t>937121148</t>
+        </is>
+      </c>
+      <c r="L558" s="2" t="inlineStr"/>
+      <c r="M558" s="2" t="inlineStr">
+        <is>
+          <t>qdq_2026</t>
+        </is>
+      </c>
+      <c r="N558" s="2" t="inlineStr"/>
+      <c r="O558" s="2" t="inlineStr"/>
+      <c r="P558" s="2" t="inlineStr">
+        <is>
+          <t>Avinguda de Barberà 309</t>
+        </is>
+      </c>
+      <c r="Q558" s="2" t="inlineStr"/>
+    </row>
+    <row r="559">
+      <c r="A559" s="3" t="inlineStr"/>
+      <c r="B559" s="3" t="inlineStr">
+        <is>
+          <t>Avinguda de Matadepera</t>
+        </is>
+      </c>
+      <c r="C559" s="3" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D559" s="3" t="inlineStr">
+        <is>
+          <t>Herboristeria AV Matadepera 43</t>
+        </is>
+      </c>
+      <c r="E559" s="3" t="inlineStr">
+        <is>
+          <t>Herboristeries</t>
+        </is>
+      </c>
+      <c r="F559" s="3" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G559" s="3" t="inlineStr">
+        <is>
+          <t>Herboristeries</t>
+        </is>
+      </c>
+      <c r="H559" s="3" t="inlineStr">
+        <is>
+          <t>41.564</t>
+        </is>
+      </c>
+      <c r="I559" s="3" t="inlineStr">
+        <is>
+          <t>2.0905</t>
+        </is>
+      </c>
+      <c r="J559" s="3" t="inlineStr"/>
+      <c r="K559" s="3" t="inlineStr">
+        <is>
+          <t>937243805</t>
+        </is>
+      </c>
+      <c r="L559" s="3" t="inlineStr"/>
+      <c r="M559" s="3" t="inlineStr">
+        <is>
+          <t>qdq_2026</t>
+        </is>
+      </c>
+      <c r="N559" s="3" t="inlineStr"/>
+      <c r="O559" s="3" t="inlineStr"/>
+      <c r="P559" s="3" t="inlineStr">
+        <is>
+          <t>Avinguda de Matadepera 43</t>
+        </is>
+      </c>
+      <c r="Q559" s="3" t="inlineStr"/>
+    </row>
+    <row r="560">
+      <c r="A560" s="2" t="inlineStr"/>
+      <c r="B560" s="2" t="inlineStr">
+        <is>
+          <t>Carretera de Barcelona</t>
+        </is>
+      </c>
+      <c r="C560" s="2" t="inlineStr">
+        <is>
+          <t>681</t>
+        </is>
+      </c>
+      <c r="D560" s="2" t="inlineStr">
+        <is>
+          <t>Vallesvisio Òptica</t>
+        </is>
+      </c>
+      <c r="E560" s="2" t="inlineStr">
+        <is>
+          <t>Salut - Òptica</t>
+        </is>
+      </c>
+      <c r="F560" s="2" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G560" s="2" t="inlineStr">
+        <is>
+          <t>Salut - Òptica</t>
+        </is>
+      </c>
+      <c r="H560" s="2" t="inlineStr">
+        <is>
+          <t>41.5395</t>
+        </is>
+      </c>
+      <c r="I560" s="2" t="inlineStr">
+        <is>
+          <t>2.1095</t>
+        </is>
+      </c>
+      <c r="J560" s="2" t="inlineStr"/>
+      <c r="K560" s="2" t="inlineStr"/>
+      <c r="L560" s="2" t="inlineStr"/>
+      <c r="M560" s="2" t="inlineStr">
+        <is>
+          <t>qdq_2026</t>
+        </is>
+      </c>
+      <c r="N560" s="2" t="inlineStr"/>
+      <c r="O560" s="2" t="inlineStr"/>
+      <c r="P560" s="2" t="inlineStr">
+        <is>
+          <t>Carretera de Barcelona 681</t>
+        </is>
+      </c>
+      <c r="Q560" s="2" t="inlineStr"/>
+    </row>
+    <row r="561">
+      <c r="A561" s="3" t="inlineStr"/>
+      <c r="B561" s="3" t="inlineStr">
+        <is>
+          <t>Avinguda de Matadepera</t>
+        </is>
+      </c>
+      <c r="C561" s="3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D561" s="3" t="inlineStr">
+        <is>
+          <t>General Òptica Matadepera</t>
+        </is>
+      </c>
+      <c r="E561" s="3" t="inlineStr">
+        <is>
+          <t>Salut - Òptica</t>
+        </is>
+      </c>
+      <c r="F561" s="3" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G561" s="3" t="inlineStr">
+        <is>
+          <t>Salut - Òptica</t>
+        </is>
+      </c>
+      <c r="H561" s="3" t="inlineStr">
+        <is>
+          <t>41.564</t>
+        </is>
+      </c>
+      <c r="I561" s="3" t="inlineStr">
+        <is>
+          <t>2.0905</t>
+        </is>
+      </c>
+      <c r="J561" s="3" t="inlineStr">
+        <is>
+          <t>generaloptica.es</t>
+        </is>
+      </c>
+      <c r="K561" s="3" t="inlineStr"/>
+      <c r="L561" s="3" t="inlineStr"/>
+      <c r="M561" s="3" t="inlineStr">
+        <is>
+          <t>qdq_2026</t>
+        </is>
+      </c>
+      <c r="N561" s="3" t="inlineStr"/>
+      <c r="O561" s="3" t="inlineStr"/>
+      <c r="P561" s="3" t="inlineStr">
+        <is>
+          <t>Avinguda de Matadepera 22</t>
+        </is>
+      </c>
+      <c r="Q561" s="3" t="inlineStr"/>
+    </row>
+    <row r="562">
+      <c r="A562" s="2" t="inlineStr"/>
+      <c r="B562" s="2" t="inlineStr">
+        <is>
+          <t>Avinguda de Matadepera</t>
+        </is>
+      </c>
+      <c r="C562" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D562" s="2" t="inlineStr">
+        <is>
+          <t>Multiopticas Optima</t>
+        </is>
+      </c>
+      <c r="E562" s="2" t="inlineStr">
+        <is>
+          <t>Salut - Òptica</t>
+        </is>
+      </c>
+      <c r="F562" s="2" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G562" s="2" t="inlineStr">
+        <is>
+          <t>Salut - Òptica</t>
+        </is>
+      </c>
+      <c r="H562" s="2" t="inlineStr">
+        <is>
+          <t>41.5475</t>
+        </is>
+      </c>
+      <c r="I562" s="2" t="inlineStr">
+        <is>
+          <t>2.107</t>
+        </is>
+      </c>
+      <c r="J562" s="2" t="inlineStr">
+        <is>
+          <t>multiopticas.com</t>
+        </is>
+      </c>
+      <c r="K562" s="2" t="inlineStr"/>
+      <c r="L562" s="2" t="inlineStr"/>
+      <c r="M562" s="2" t="inlineStr">
+        <is>
+          <t>qdq_2026</t>
+        </is>
+      </c>
+      <c r="N562" s="2" t="inlineStr"/>
+      <c r="O562" s="2" t="inlineStr"/>
+      <c r="P562" s="2" t="inlineStr">
+        <is>
+          <t>Avinguda de Matadepera 74</t>
+        </is>
+      </c>
+      <c r="Q562" s="2" t="inlineStr"/>
+    </row>
+    <row r="563">
+      <c r="A563" s="3" t="inlineStr"/>
+      <c r="B563" s="3" t="inlineStr">
+        <is>
+          <t>Rambla Sabadell</t>
+        </is>
+      </c>
+      <c r="C563" s="3" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="D563" s="3" t="inlineStr">
+        <is>
+          <t>Óptica Guffo</t>
+        </is>
+      </c>
+      <c r="E563" s="3" t="inlineStr">
+        <is>
+          <t>Salut - Òptica</t>
+        </is>
+      </c>
+      <c r="F563" s="3" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G563" s="3" t="inlineStr">
+        <is>
+          <t>Salut - Òptica</t>
+        </is>
+      </c>
+      <c r="H563" s="3" t="inlineStr">
+        <is>
+          <t>41.5475</t>
+        </is>
+      </c>
+      <c r="I563" s="3" t="inlineStr">
+        <is>
+          <t>2.107</t>
+        </is>
+      </c>
+      <c r="J563" s="3" t="inlineStr"/>
+      <c r="K563" s="3" t="inlineStr"/>
+      <c r="L563" s="3" t="inlineStr"/>
+      <c r="M563" s="3" t="inlineStr">
+        <is>
+          <t>qdq_2026</t>
+        </is>
+      </c>
+      <c r="N563" s="3" t="inlineStr"/>
+      <c r="O563" s="3" t="inlineStr"/>
+      <c r="P563" s="3" t="inlineStr">
+        <is>
+          <t>Rambla Sabadell 213</t>
+        </is>
+      </c>
+      <c r="Q563" s="3" t="inlineStr"/>
+    </row>
+    <row r="564">
+      <c r="A564" s="2" t="inlineStr"/>
+      <c r="B564" s="2" t="inlineStr">
+        <is>
+          <t>Ronda Zamenhof</t>
+        </is>
+      </c>
+      <c r="C564" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D564" s="2" t="inlineStr">
+        <is>
+          <t>L'Òptica Zamenhof</t>
+        </is>
+      </c>
+      <c r="E564" s="2" t="inlineStr">
+        <is>
+          <t>Salut - Òptica</t>
+        </is>
+      </c>
+      <c r="F564" s="2" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G564" s="2" t="inlineStr">
+        <is>
+          <t>Salut - Òptica</t>
+        </is>
+      </c>
+      <c r="H564" s="2" t="inlineStr">
+        <is>
+          <t>41.5605</t>
+        </is>
+      </c>
+      <c r="I564" s="2" t="inlineStr">
+        <is>
+          <t>2.1025</t>
+        </is>
+      </c>
+      <c r="J564" s="2" t="inlineStr"/>
+      <c r="K564" s="2" t="inlineStr"/>
+      <c r="L564" s="2" t="inlineStr"/>
+      <c r="M564" s="2" t="inlineStr">
+        <is>
+          <t>qdq_2026</t>
+        </is>
+      </c>
+      <c r="N564" s="2" t="inlineStr"/>
+      <c r="O564" s="2" t="inlineStr"/>
+      <c r="P564" s="2" t="inlineStr">
+        <is>
+          <t>Ronda Zamenhof 50</t>
+        </is>
+      </c>
+      <c r="Q564" s="2" t="inlineStr"/>
+    </row>
+    <row r="565">
+      <c r="A565" s="3" t="inlineStr"/>
+      <c r="B565" s="3" t="inlineStr">
+        <is>
+          <t>Carretera de Terrassa</t>
+        </is>
+      </c>
+      <c r="C565" s="3" t="inlineStr">
+        <is>
+          <t>389</t>
+        </is>
+      </c>
+      <c r="D565" s="3" t="inlineStr">
+        <is>
+          <t>DOSÒPTICS</t>
+        </is>
+      </c>
+      <c r="E565" s="3" t="inlineStr">
+        <is>
+          <t>Salut - Òptica</t>
+        </is>
+      </c>
+      <c r="F565" s="3" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G565" s="3" t="inlineStr">
+        <is>
+          <t>Salut - Òptica</t>
+        </is>
+      </c>
+      <c r="H565" s="3" t="inlineStr">
+        <is>
+          <t>41.553</t>
+        </is>
+      </c>
+      <c r="I565" s="3" t="inlineStr">
+        <is>
+          <t>2.0875</t>
+        </is>
+      </c>
+      <c r="J565" s="3" t="inlineStr"/>
+      <c r="K565" s="3" t="inlineStr"/>
+      <c r="L565" s="3" t="inlineStr"/>
+      <c r="M565" s="3" t="inlineStr">
+        <is>
+          <t>qdq_2026</t>
+        </is>
+      </c>
+      <c r="N565" s="3" t="inlineStr"/>
+      <c r="O565" s="3" t="inlineStr"/>
+      <c r="P565" s="3" t="inlineStr">
+        <is>
+          <t>Carretera de Terrassa 389</t>
+        </is>
+      </c>
+      <c r="Q565" s="3" t="inlineStr"/>
+    </row>
+    <row r="566">
+      <c r="A566" s="2" t="inlineStr"/>
+      <c r="B566" s="2" t="inlineStr">
+        <is>
+          <t>Carrer de Lluçanès</t>
+        </is>
+      </c>
+      <c r="C566" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D566" s="2" t="inlineStr">
+        <is>
+          <t>RM Optics</t>
+        </is>
+      </c>
+      <c r="E566" s="2" t="inlineStr">
+        <is>
+          <t>Salut - Òptica</t>
+        </is>
+      </c>
+      <c r="F566" s="2" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G566" s="2" t="inlineStr">
+        <is>
+          <t>Salut - Òptica</t>
+        </is>
+      </c>
+      <c r="H566" s="2" t="inlineStr">
+        <is>
+          <t>41.564</t>
+        </is>
+      </c>
+      <c r="I566" s="2" t="inlineStr">
+        <is>
+          <t>2.0905</t>
+        </is>
+      </c>
+      <c r="J566" s="2" t="inlineStr"/>
+      <c r="K566" s="2" t="inlineStr"/>
+      <c r="L566" s="2" t="inlineStr"/>
+      <c r="M566" s="2" t="inlineStr">
+        <is>
+          <t>qdq_2026</t>
+        </is>
+      </c>
+      <c r="N566" s="2" t="inlineStr"/>
+      <c r="O566" s="2" t="inlineStr"/>
+      <c r="P566" s="2" t="inlineStr">
+        <is>
+          <t>Carrer de Lluçanès 4</t>
+        </is>
+      </c>
+      <c r="Q566" s="2" t="inlineStr"/>
+    </row>
+    <row r="567">
+      <c r="A567" s="3" t="inlineStr"/>
+      <c r="B567" s="3" t="inlineStr">
+        <is>
+          <t>Avinguda de Francesc Macià</t>
+        </is>
+      </c>
+      <c r="C567" s="3" t="inlineStr">
+        <is>
+          <t>46-48</t>
+        </is>
+      </c>
+      <c r="D567" s="3" t="inlineStr">
+        <is>
+          <t>Serra García Òptica</t>
+        </is>
+      </c>
+      <c r="E567" s="3" t="inlineStr">
+        <is>
+          <t>Salut - Òptica</t>
+        </is>
+      </c>
+      <c r="F567" s="3" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G567" s="3" t="inlineStr">
+        <is>
+          <t>Salut - Òptica</t>
+        </is>
+      </c>
+      <c r="H567" s="3" t="inlineStr">
+        <is>
+          <t>41.5605</t>
+        </is>
+      </c>
+      <c r="I567" s="3" t="inlineStr">
+        <is>
+          <t>2.1025</t>
+        </is>
+      </c>
+      <c r="J567" s="3" t="inlineStr"/>
+      <c r="K567" s="3" t="inlineStr"/>
+      <c r="L567" s="3" t="inlineStr"/>
+      <c r="M567" s="3" t="inlineStr">
+        <is>
+          <t>qdq_2026</t>
+        </is>
+      </c>
+      <c r="N567" s="3" t="inlineStr"/>
+      <c r="O567" s="3" t="inlineStr"/>
+      <c r="P567" s="3" t="inlineStr">
+        <is>
+          <t>Avinguda de Francesc Macià 46-48</t>
+        </is>
+      </c>
+      <c r="Q567" s="3" t="inlineStr"/>
+    </row>
+    <row r="568">
+      <c r="A568" s="2" t="inlineStr"/>
+      <c r="B568" s="2" t="inlineStr"/>
+      <c r="C568" s="2" t="inlineStr"/>
+      <c r="D568" s="2" t="inlineStr">
+        <is>
+          <t>Centre d'Atenció Primària Sant Oleguer</t>
+        </is>
+      </c>
+      <c r="E568" s="2" t="inlineStr">
+        <is>
+          <t>Salut - Medicina</t>
+        </is>
+      </c>
+      <c r="F568" s="2" t="inlineStr"/>
+      <c r="G568" s="2" t="inlineStr">
+        <is>
+          <t>Activitats de medicina especialitzada</t>
+        </is>
+      </c>
+      <c r="H568" s="2" t="inlineStr">
+        <is>
+          <t>41.5385552</t>
+        </is>
+      </c>
+      <c r="I568" s="2" t="inlineStr">
+        <is>
+          <t>2.1179282</t>
+        </is>
+      </c>
+      <c r="J568" s="2" t="inlineStr"/>
+      <c r="K568" s="2" t="inlineStr"/>
+      <c r="L568" s="2" t="inlineStr"/>
+      <c r="M568" s="2" t="inlineStr">
+        <is>
+          <t>OSM_2026</t>
+        </is>
+      </c>
+      <c r="N568" s="2" t="inlineStr"/>
+      <c r="O568" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P568" s="2" t="inlineStr"/>
+      <c r="Q568" s="2" t="inlineStr"/>
+    </row>
+    <row r="569">
+      <c r="A569" s="3" t="inlineStr"/>
+      <c r="B569" s="3" t="inlineStr"/>
+      <c r="C569" s="3" t="inlineStr"/>
+      <c r="D569" s="3" t="inlineStr">
+        <is>
+          <t>Asepeyo</t>
+        </is>
+      </c>
+      <c r="E569" s="3" t="inlineStr">
+        <is>
+          <t>Salut - Medicina</t>
+        </is>
+      </c>
+      <c r="F569" s="3" t="inlineStr"/>
+      <c r="G569" s="3" t="inlineStr">
+        <is>
+          <t>Activitats de medicina especialitzada</t>
+        </is>
+      </c>
+      <c r="H569" s="3" t="inlineStr">
+        <is>
+          <t>41.5447489</t>
+        </is>
+      </c>
+      <c r="I569" s="3" t="inlineStr">
+        <is>
+          <t>2.1002579</t>
+        </is>
+      </c>
+      <c r="J569" s="3" t="inlineStr"/>
+      <c r="K569" s="3" t="inlineStr"/>
+      <c r="L569" s="3" t="inlineStr"/>
+      <c r="M569" s="3" t="inlineStr">
+        <is>
+          <t>OSM_2026</t>
+        </is>
+      </c>
+      <c r="N569" s="3" t="inlineStr"/>
+      <c r="O569" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P569" s="3" t="inlineStr"/>
+      <c r="Q569" s="3" t="inlineStr"/>
+    </row>
+    <row r="570">
+      <c r="A570" s="2" t="inlineStr"/>
+      <c r="B570" s="2" t="inlineStr"/>
+      <c r="C570" s="2" t="inlineStr"/>
+      <c r="D570" s="2" t="inlineStr">
+        <is>
+          <t>C.A.P. Sant Fèlix</t>
+        </is>
+      </c>
+      <c r="E570" s="2" t="inlineStr">
+        <is>
+          <t>Salut - Medicina</t>
+        </is>
+      </c>
+      <c r="F570" s="2" t="inlineStr"/>
+      <c r="G570" s="2" t="inlineStr">
+        <is>
+          <t>Activitats de medicina especialitzada</t>
+        </is>
+      </c>
+      <c r="H570" s="2" t="inlineStr">
+        <is>
+          <t>41.5325822</t>
+        </is>
+      </c>
+      <c r="I570" s="2" t="inlineStr">
+        <is>
+          <t>2.1139605</t>
+        </is>
+      </c>
+      <c r="J570" s="2" t="inlineStr"/>
+      <c r="K570" s="2" t="inlineStr"/>
+      <c r="L570" s="2" t="inlineStr"/>
+      <c r="M570" s="2" t="inlineStr">
+        <is>
+          <t>OSM_2026</t>
+        </is>
+      </c>
+      <c r="N570" s="2" t="inlineStr"/>
+      <c r="O570" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P570" s="2" t="inlineStr"/>
+      <c r="Q570" s="2" t="inlineStr"/>
+    </row>
+    <row r="571">
+      <c r="A571" s="3" t="inlineStr"/>
+      <c r="B571" s="3" t="inlineStr"/>
+      <c r="C571" s="3" t="inlineStr"/>
+      <c r="D571" s="3" t="inlineStr">
+        <is>
+          <t>Multiópticas</t>
+        </is>
+      </c>
+      <c r="E571" s="3" t="inlineStr">
+        <is>
+          <t>Salut - Òptica</t>
+        </is>
+      </c>
+      <c r="F571" s="3" t="inlineStr">
+        <is>
+          <t>optician</t>
+        </is>
+      </c>
+      <c r="G571" s="3" t="inlineStr">
+        <is>
+          <t>Òptica</t>
+        </is>
+      </c>
+      <c r="H571" s="3" t="inlineStr">
+        <is>
+          <t>41.5412052</t>
+        </is>
+      </c>
+      <c r="I571" s="3" t="inlineStr">
+        <is>
+          <t>2.1117753</t>
+        </is>
+      </c>
+      <c r="J571" s="3" t="inlineStr"/>
+      <c r="K571" s="3" t="inlineStr"/>
+      <c r="L571" s="3" t="inlineStr"/>
+      <c r="M571" s="3" t="inlineStr">
+        <is>
+          <t>OSM</t>
+        </is>
+      </c>
+      <c r="N571" s="3" t="inlineStr"/>
+      <c r="O571" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P571" s="3" t="inlineStr"/>
+      <c r="Q571" s="3" t="inlineStr"/>
+    </row>
+    <row r="572">
+      <c r="A572" s="2" t="inlineStr"/>
+      <c r="B572" s="2" t="inlineStr"/>
+      <c r="C572" s="2" t="inlineStr"/>
+      <c r="D572" s="2" t="inlineStr">
+        <is>
+          <t>Visionlab</t>
+        </is>
+      </c>
+      <c r="E572" s="2" t="inlineStr">
+        <is>
+          <t>Salut - Òptica</t>
+        </is>
+      </c>
+      <c r="F572" s="2" t="inlineStr">
+        <is>
+          <t>optician</t>
+        </is>
+      </c>
+      <c r="G572" s="2" t="inlineStr">
+        <is>
+          <t>Òptica</t>
+        </is>
+      </c>
+      <c r="H572" s="2" t="inlineStr">
+        <is>
+          <t>41.5535969</t>
+        </is>
+      </c>
+      <c r="I572" s="2" t="inlineStr">
+        <is>
+          <t>2.0985035</t>
+        </is>
+      </c>
+      <c r="J572" s="2" t="inlineStr"/>
+      <c r="K572" s="2" t="inlineStr"/>
+      <c r="L572" s="2" t="inlineStr"/>
+      <c r="M572" s="2" t="inlineStr">
+        <is>
+          <t>OSM</t>
+        </is>
+      </c>
+      <c r="N572" s="2" t="inlineStr"/>
+      <c r="O572" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P572" s="2" t="inlineStr"/>
+      <c r="Q572" s="2" t="inlineStr"/>
+    </row>
+    <row r="573">
+      <c r="A573" s="3" t="inlineStr"/>
+      <c r="B573" s="3" t="inlineStr"/>
+      <c r="C573" s="3" t="inlineStr"/>
+      <c r="D573" s="3" t="inlineStr">
+        <is>
+          <t>FIOSTEC Funcional Sabadell</t>
+        </is>
+      </c>
+      <c r="E573" s="3" t="inlineStr">
+        <is>
+          <t>Salut - Fisioterapia</t>
+        </is>
+      </c>
+      <c r="F573" s="3" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G573" s="3" t="inlineStr">
+        <is>
+          <t>Salut - Fisioterapia</t>
+        </is>
+      </c>
+      <c r="H573" s="3" t="inlineStr">
+        <is>
+          <t>41.5485</t>
+        </is>
+      </c>
+      <c r="I573" s="3" t="inlineStr">
+        <is>
+          <t>2.109</t>
+        </is>
+      </c>
+      <c r="J573" s="3" t="inlineStr">
+        <is>
+          <t>fiostec.com</t>
+        </is>
+      </c>
+      <c r="K573" s="3" t="inlineStr"/>
+      <c r="L573" s="3" t="inlineStr"/>
+      <c r="M573" s="3" t="inlineStr">
+        <is>
+          <t>WebSearch_2026</t>
+        </is>
+      </c>
+      <c r="N573" s="3" t="inlineStr"/>
+      <c r="O573" s="3" t="inlineStr"/>
+      <c r="P573" s="3" t="inlineStr"/>
+      <c r="Q573" s="3" t="inlineStr"/>
+    </row>
+    <row r="574">
+      <c r="A574" s="2" t="inlineStr"/>
+      <c r="B574" s="2" t="inlineStr"/>
+      <c r="C574" s="2" t="inlineStr"/>
+      <c r="D574" s="2" t="inlineStr">
+        <is>
+          <t>Fisioterapia i Osteopatia Sabadell</t>
+        </is>
+      </c>
+      <c r="E574" s="2" t="inlineStr">
+        <is>
+          <t>Salut - Fisioterapia</t>
+        </is>
+      </c>
+      <c r="F574" s="2" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G574" s="2" t="inlineStr">
+        <is>
+          <t>Salut - Fisioterapia</t>
+        </is>
+      </c>
+      <c r="H574" s="2" t="inlineStr">
+        <is>
+          <t>41.5485</t>
+        </is>
+      </c>
+      <c r="I574" s="2" t="inlineStr">
+        <is>
+          <t>2.109</t>
+        </is>
+      </c>
+      <c r="J574" s="2" t="inlineStr">
+        <is>
+          <t>fisioterapiaiosteopatia.net</t>
+        </is>
+      </c>
+      <c r="K574" s="2" t="inlineStr"/>
+      <c r="L574" s="2" t="inlineStr"/>
+      <c r="M574" s="2" t="inlineStr">
+        <is>
+          <t>WebSearch_2026</t>
+        </is>
+      </c>
+      <c r="N574" s="2" t="inlineStr"/>
+      <c r="O574" s="2" t="inlineStr"/>
+      <c r="P574" s="2" t="inlineStr"/>
+      <c r="Q574" s="2" t="inlineStr"/>
+    </row>
+    <row r="575">
+      <c r="A575" s="3" t="inlineStr"/>
+      <c r="B575" s="3" t="inlineStr"/>
+      <c r="C575" s="3" t="inlineStr"/>
+      <c r="D575" s="3" t="inlineStr">
+        <is>
+          <t>PsicoSabadell</t>
+        </is>
+      </c>
+      <c r="E575" s="3" t="inlineStr">
+        <is>
+          <t>Salut - Psicologia</t>
+        </is>
+      </c>
+      <c r="F575" s="3" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G575" s="3" t="inlineStr">
+        <is>
+          <t>Salut - Psicologia</t>
+        </is>
+      </c>
+      <c r="H575" s="3" t="inlineStr">
+        <is>
+          <t>41.5485</t>
+        </is>
+      </c>
+      <c r="I575" s="3" t="inlineStr">
+        <is>
+          <t>2.109</t>
+        </is>
+      </c>
+      <c r="J575" s="3" t="inlineStr">
+        <is>
+          <t>psicosabadell.com</t>
+        </is>
+      </c>
+      <c r="K575" s="3" t="inlineStr"/>
+      <c r="L575" s="3" t="inlineStr"/>
+      <c r="M575" s="3" t="inlineStr">
+        <is>
+          <t>WebSearch_2026</t>
+        </is>
+      </c>
+      <c r="N575" s="3" t="inlineStr"/>
+      <c r="O575" s="3" t="inlineStr"/>
+      <c r="P575" s="3" t="inlineStr"/>
+      <c r="Q575" s="3" t="inlineStr"/>
+    </row>
+    <row r="576">
+      <c r="A576" s="2" t="inlineStr"/>
+      <c r="B576" s="2" t="inlineStr"/>
+      <c r="C576" s="2" t="inlineStr"/>
+      <c r="D576" s="2" t="inlineStr">
+        <is>
+          <t>Psicologia Clínica Sabadell</t>
+        </is>
+      </c>
+      <c r="E576" s="2" t="inlineStr">
+        <is>
+          <t>Salut - Psicologia</t>
+        </is>
+      </c>
+      <c r="F576" s="2" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G576" s="2" t="inlineStr">
+        <is>
+          <t>Salut - Psicologia</t>
+        </is>
+      </c>
+      <c r="H576" s="2" t="inlineStr">
+        <is>
+          <t>41.5485</t>
+        </is>
+      </c>
+      <c r="I576" s="2" t="inlineStr">
+        <is>
+          <t>2.109</t>
+        </is>
+      </c>
+      <c r="J576" s="2" t="inlineStr">
+        <is>
+          <t>psicologiaclinicasabadell.es</t>
+        </is>
+      </c>
+      <c r="K576" s="2" t="inlineStr"/>
+      <c r="L576" s="2" t="inlineStr"/>
+      <c r="M576" s="2" t="inlineStr">
+        <is>
+          <t>WebSearch_2026</t>
+        </is>
+      </c>
+      <c r="N576" s="2" t="inlineStr"/>
+      <c r="O576" s="2" t="inlineStr"/>
+      <c r="P576" s="2" t="inlineStr"/>
+      <c r="Q576" s="2" t="inlineStr"/>
+    </row>
+    <row r="577">
+      <c r="A577" s="3" t="inlineStr"/>
+      <c r="B577" s="3" t="inlineStr"/>
+      <c r="C577" s="3" t="inlineStr"/>
+      <c r="D577" s="3" t="inlineStr">
+        <is>
+          <t>Psicologia i Educació Sabadell</t>
+        </is>
+      </c>
+      <c r="E577" s="3" t="inlineStr">
+        <is>
+          <t>Salut - Psicologia</t>
+        </is>
+      </c>
+      <c r="F577" s="3" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G577" s="3" t="inlineStr">
+        <is>
+          <t>Salut - Psicologia</t>
+        </is>
+      </c>
+      <c r="H577" s="3" t="inlineStr">
+        <is>
+          <t>41.5485</t>
+        </is>
+      </c>
+      <c r="I577" s="3" t="inlineStr">
+        <is>
+          <t>2.109</t>
+        </is>
+      </c>
+      <c r="J577" s="3" t="inlineStr">
+        <is>
+          <t>psicologiaieducaciosabadell.com</t>
+        </is>
+      </c>
+      <c r="K577" s="3" t="inlineStr"/>
+      <c r="L577" s="3" t="inlineStr"/>
+      <c r="M577" s="3" t="inlineStr">
+        <is>
+          <t>WebSearch_2026</t>
+        </is>
+      </c>
+      <c r="N577" s="3" t="inlineStr"/>
+      <c r="O577" s="3" t="inlineStr"/>
+      <c r="P577" s="3" t="inlineStr"/>
+      <c r="Q577" s="3" t="inlineStr"/>
+    </row>
+    <row r="578">
+      <c r="A578" s="2" t="inlineStr"/>
+      <c r="B578" s="2" t="inlineStr"/>
+      <c r="C578" s="2" t="inlineStr"/>
+      <c r="D578" s="2" t="inlineStr">
+        <is>
+          <t>Mèdic Dental Sabadell</t>
+        </is>
+      </c>
+      <c r="E578" s="2" t="inlineStr">
+        <is>
+          <t>Salut - Dental</t>
+        </is>
+      </c>
+      <c r="F578" s="2" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G578" s="2" t="inlineStr">
+        <is>
+          <t>Salut - Dental</t>
+        </is>
+      </c>
+      <c r="H578" s="2" t="inlineStr">
+        <is>
+          <t>41.5485</t>
+        </is>
+      </c>
+      <c r="I578" s="2" t="inlineStr">
+        <is>
+          <t>2.109</t>
+        </is>
+      </c>
+      <c r="J578" s="2" t="inlineStr">
+        <is>
+          <t>medicdentalsabadell.com</t>
+        </is>
+      </c>
+      <c r="K578" s="2" t="inlineStr"/>
+      <c r="L578" s="2" t="inlineStr"/>
+      <c r="M578" s="2" t="inlineStr">
+        <is>
+          <t>WebSearch_2026</t>
+        </is>
+      </c>
+      <c r="N578" s="2" t="inlineStr"/>
+      <c r="O578" s="2" t="inlineStr"/>
+      <c r="P578" s="2" t="inlineStr"/>
+      <c r="Q578" s="2" t="inlineStr"/>
+    </row>
+    <row r="579">
+      <c r="A579" s="3" t="inlineStr"/>
+      <c r="B579" s="3" t="inlineStr"/>
+      <c r="C579" s="3" t="inlineStr"/>
+      <c r="D579" s="3" t="inlineStr">
+        <is>
+          <t>Inidental Sabadell</t>
+        </is>
+      </c>
+      <c r="E579" s="3" t="inlineStr">
+        <is>
+          <t>Salut - Dental</t>
+        </is>
+      </c>
+      <c r="F579" s="3" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G579" s="3" t="inlineStr">
+        <is>
+          <t>Salut - Dental</t>
+        </is>
+      </c>
+      <c r="H579" s="3" t="inlineStr">
+        <is>
+          <t>41.5485</t>
+        </is>
+      </c>
+      <c r="I579" s="3" t="inlineStr">
+        <is>
+          <t>2.109</t>
+        </is>
+      </c>
+      <c r="J579" s="3" t="inlineStr">
+        <is>
+          <t>inidental.com</t>
+        </is>
+      </c>
+      <c r="K579" s="3" t="inlineStr"/>
+      <c r="L579" s="3" t="inlineStr"/>
+      <c r="M579" s="3" t="inlineStr">
+        <is>
+          <t>WebSearch_2026</t>
+        </is>
+      </c>
+      <c r="N579" s="3" t="inlineStr"/>
+      <c r="O579" s="3" t="inlineStr"/>
+      <c r="P579" s="3" t="inlineStr"/>
+      <c r="Q579" s="3" t="inlineStr"/>
+    </row>
+    <row r="580">
+      <c r="A580" s="2" t="inlineStr"/>
+      <c r="B580" s="2" t="inlineStr"/>
+      <c r="C580" s="2" t="inlineStr"/>
+      <c r="D580" s="2" t="inlineStr">
+        <is>
+          <t>Centro Médico del Vallès, S.L.</t>
+        </is>
+      </c>
+      <c r="E580" s="2" t="inlineStr">
+        <is>
+          <t>Salut - Medicina</t>
+        </is>
+      </c>
+      <c r="F580" s="2" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G580" s="2" t="inlineStr">
+        <is>
+          <t>Salut - Medicina</t>
+        </is>
+      </c>
+      <c r="H580" s="2" t="inlineStr">
+        <is>
+          <t>41.5485</t>
+        </is>
+      </c>
+      <c r="I580" s="2" t="inlineStr">
+        <is>
+          <t>2.109</t>
+        </is>
+      </c>
+      <c r="J580" s="2" t="inlineStr"/>
+      <c r="K580" s="2" t="inlineStr"/>
+      <c r="L580" s="2" t="inlineStr"/>
+      <c r="M580" s="2" t="inlineStr">
+        <is>
+          <t>WebSearch_2026</t>
+        </is>
+      </c>
+      <c r="N580" s="2" t="inlineStr"/>
+      <c r="O580" s="2" t="inlineStr"/>
+      <c r="P580" s="2" t="inlineStr"/>
+      <c r="Q580" s="2" t="inlineStr"/>
+    </row>
+    <row r="581">
+      <c r="A581" s="3" t="inlineStr"/>
+      <c r="B581" s="3" t="inlineStr"/>
+      <c r="C581" s="3" t="inlineStr"/>
+      <c r="D581" s="3" t="inlineStr">
+        <is>
+          <t>NAEKO S.L.</t>
+        </is>
+      </c>
+      <c r="E581" s="3" t="inlineStr">
+        <is>
+          <t>Salut - Medicina</t>
+        </is>
+      </c>
+      <c r="F581" s="3" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G581" s="3" t="inlineStr">
+        <is>
+          <t>Salut - Medicina</t>
+        </is>
+      </c>
+      <c r="H581" s="3" t="inlineStr">
+        <is>
+          <t>41.5485</t>
+        </is>
+      </c>
+      <c r="I581" s="3" t="inlineStr">
+        <is>
+          <t>2.109</t>
+        </is>
+      </c>
+      <c r="J581" s="3" t="inlineStr"/>
+      <c r="K581" s="3" t="inlineStr"/>
+      <c r="L581" s="3" t="inlineStr"/>
+      <c r="M581" s="3" t="inlineStr">
+        <is>
+          <t>WebSearch_2026</t>
+        </is>
+      </c>
+      <c r="N581" s="3" t="inlineStr"/>
+      <c r="O581" s="3" t="inlineStr"/>
+      <c r="P581" s="3" t="inlineStr"/>
+      <c r="Q581" s="3" t="inlineStr"/>
+    </row>
+    <row r="582">
+      <c r="A582" s="2" t="inlineStr"/>
+      <c r="B582" s="2" t="inlineStr"/>
+      <c r="C582" s="2" t="inlineStr"/>
+      <c r="D582" s="2" t="inlineStr">
+        <is>
+          <t>Trauma Salut</t>
+        </is>
+      </c>
+      <c r="E582" s="2" t="inlineStr">
+        <is>
+          <t>Salut - Medicina</t>
+        </is>
+      </c>
+      <c r="F582" s="2" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G582" s="2" t="inlineStr">
+        <is>
+          <t>Salut - Medicina</t>
+        </is>
+      </c>
+      <c r="H582" s="2" t="inlineStr">
+        <is>
+          <t>41.5485</t>
+        </is>
+      </c>
+      <c r="I582" s="2" t="inlineStr">
+        <is>
+          <t>2.109</t>
+        </is>
+      </c>
+      <c r="J582" s="2" t="inlineStr"/>
+      <c r="K582" s="2" t="inlineStr"/>
+      <c r="L582" s="2" t="inlineStr"/>
+      <c r="M582" s="2" t="inlineStr">
+        <is>
+          <t>WebSearch_2026</t>
+        </is>
+      </c>
+      <c r="N582" s="2" t="inlineStr"/>
+      <c r="O582" s="2" t="inlineStr"/>
+      <c r="P582" s="2" t="inlineStr"/>
+      <c r="Q582" s="2" t="inlineStr"/>
+    </row>
+    <row r="583">
+      <c r="A583" s="3" t="inlineStr"/>
+      <c r="B583" s="3" t="inlineStr"/>
+      <c r="C583" s="3" t="inlineStr"/>
+      <c r="D583" s="3" t="inlineStr">
+        <is>
+          <t>Bailcas Ortopèdia Sabadell</t>
+        </is>
+      </c>
+      <c r="E583" s="3" t="inlineStr">
+        <is>
+          <t>Salut - Ortopèdia</t>
+        </is>
+      </c>
+      <c r="F583" s="3" t="inlineStr">
+        <is>
+          <t>WebSearch</t>
+        </is>
+      </c>
+      <c r="G583" s="3" t="inlineStr">
+        <is>
+          <t>Salut - Ortopèdia</t>
+        </is>
+      </c>
+      <c r="H583" s="3" t="inlineStr">
+        <is>
+          <t>41.5485</t>
+        </is>
+      </c>
+      <c r="I583" s="3" t="inlineStr">
+        <is>
+          <t>2.109</t>
+        </is>
+      </c>
+      <c r="J583" s="3" t="inlineStr">
+        <is>
+          <t>bailcas.com</t>
+        </is>
+      </c>
+      <c r="K583" s="3" t="inlineStr"/>
+      <c r="L583" s="3" t="inlineStr"/>
+      <c r="M583" s="3" t="inlineStr">
+        <is>
+          <t>WebSearch_2026</t>
+        </is>
+      </c>
+      <c r="N583" s="3" t="inlineStr"/>
+      <c r="O583" s="3" t="inlineStr"/>
+      <c r="P583" s="3" t="inlineStr"/>
+      <c r="Q583" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q482"/>
+  <autoFilter ref="A1:Q583"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -33190,7 +39193,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -33226,7 +39229,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>118</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4">
@@ -33236,7 +39239,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5">
@@ -33252,25 +39255,45 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Salut - Psicologia</t>
+          <t>Herboristeries</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
+          <t>Salut - Psicologia</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Salut - Ortopèdia</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
           <t>Salut - Fisioterapia</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n">
+      <c r="B9" s="3" t="n">
         <v>6</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B7"/>
+  <autoFilter ref="A1:B9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -33408,7 +39431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -33430,21 +39453,21 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>OSM</t>
+          <t>qdq_2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>119</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>qdq_2026</t>
+          <t>OSM</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>101</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4">
@@ -33454,7 +39477,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>97</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5">
@@ -33470,57 +39493,57 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>MGC Mútua</t>
+          <t>farmacias_2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Sanitas</t>
+          <t>MGC Mútua</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>dentistaentuciudad_2026</t>
+          <t>Sanitas</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>OSM_2026</t>
+          <t>dentistaentuciudad_2026</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Asisa</t>
+          <t>OSM_2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>qdq.com_2026</t>
+          <t>Asisa</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
@@ -33530,35 +39553,45 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>MGC_Mutua</t>
+          <t>qdq.com_2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>AXA Salud</t>
+          <t>MGC_Mutua</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>AXA Salud</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
           <t>web.sabadell.cat</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n">
+      <c r="B15" s="3" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B14"/>
+  <autoFilter ref="A1:B15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>